--- a/data/outreach_yc_pilot/outreach_packs.xlsx
+++ b/data/outreach_yc_pilot/outreach_packs.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outreach" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Outreach'!$A$1:$V$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Outreach'!$A$1:$AA$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V61"/>
+  <dimension ref="A1:AA61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -431,22 +431,27 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="36" customWidth="1" min="14" max="14"/>
-    <col width="56" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
-    <col width="48" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
+    <col width="36" customWidth="1" min="17" max="17"/>
+    <col width="56" customWidth="1" min="18" max="18"/>
     <col width="40" customWidth="1" min="19" max="19"/>
     <col width="40" customWidth="1" min="20" max="20"/>
-    <col width="24" customWidth="1" min="21" max="21"/>
-    <col width="48" customWidth="1" min="22" max="22"/>
+    <col width="48" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="40" customWidth="1" min="23" max="23"/>
+    <col width="32" customWidth="1" min="24" max="24"/>
+    <col width="24" customWidth="1" min="25" max="25"/>
+    <col width="28" customWidth="1" min="26" max="26"/>
+    <col width="48" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,80 +487,105 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>final_stage</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>ready_to_send</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>contact_persona</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>contact_name</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>contact_title</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>contact_email</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>contact_linkedin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>contact_source</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>hook_email</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>hook_linkedin</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>email_subject</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>email_body</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>linkedin_connection_note</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>discovery_question</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>company_summary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pain_points</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>value_props_for_them</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>disqualifier_notes</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>review_warnings</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>evidence_ids_used</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>important_urls</t>
         </is>
@@ -588,41 +618,52 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G2" t="b">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
         <v>1</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>CTO or engineering lead responsible for operations</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Edgar Babajanyan</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Co-Founder and CTO</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/edgar-babajanyan-a28230217/</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Captain's AI search capabilities can bridge the gap for teams lacking dedicated SRE resources, ensuring faster incident resolution and enhanced operational performance.</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Exploring Enhanced Incident Response with Captain</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Hi Edgar,
 With Captain's focus on scalable AI solutions for knowledge retrieval, teams may significantly enhance their operational efficiency. Captain provides a multimodal data search capability through its robust API, supporting various formats like images, videos, and documents. This could address substantial pain points you might face in managing large datasets and incident response without a full SRE team.
@@ -630,51 +671,66 @@
 How do you currently manage incident responses and knowledge retrieval for your production systems?</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Hi Edgar, I noticed Captain excels in operational efficiency through AI search—I'd like to connect and discuss strategies!</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>How do you currently manage incident responses and knowledge retrieval for your production systems?</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Captain offers an accurate knowledge search that scales for AI agents, emphasizing operational efficiency with a robust API that supports various data types including video, images, and documents.</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>• Need for efficient and accurate search capabilities in handling large amounts of data.
 • Improving operational reliability and incident response without a full SRE team.
 • Seeking scalable solutions to enhance productivity and reduce troubleshooting time.</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>• Boost incident response time and operational reliability without dedicated SRE resources.
 • Utilize advanced search capabilities tailored for production-critical systems.
 • Leverage managed storage and integrated tools to optimize data handling.</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>no_seed_email</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>ev_76bfb6f29b93, ev_a287f27976f5, ev_bf8eac541303, ev_687832e4e867</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>[fallback_page] https://auth.runcaptain.com/u/login?state=hKFo2SBReXM4T0UwVHdFc2FNaUY3NXVhbjlqbkR1bFdPYjRNUaFur3VuaXZlcnNhbC1sb2dpbqN0aWTZIENHYWdaMjcteTUyVDZmbXF1Y29XNXNFZmYtY1N1ek0to2NpZNkgbFY2bkZySUtDNUxjWXdqeUNadE1lcGpOTTRoOGhrRGI
+  Fetched from search result for additional context.
 [docs] https://docs.runcaptain.com *
+  Shows public API/integration/developer surface.
 [fallback_page] https://docs.runcaptain.com/guides/get-started/introduction
+  Fetched from search result for additional context.
 [github] https://github.com/runcaptain/captain-mrag-bench
+  Technical footprint and engineering culture.
 [status] https://status.runcaptain.com *
+  Indicates production uptime monitoring.
 [homepage] https://www.runcaptain.com/ *
+  Explains core product and target customer.
 [blog] https://www.runcaptain.com/blog
+  Product updates and engineering narrative.
 [fallback_page] https://www.runcaptain.com/pricing
-[seed_metadata] https://www.ycombinator.com/companies/captain</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/captain
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -705,29 +761,44 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G3" t="b">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>DevOps engineers or Engineering team leads</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Lark's AI-driven testing solutions enhance incident response workflows without needing a complete SRE team.</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Lark improves DevOps efficiency with AI-driven testing that adapts to changes.</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Inquiry on Incident Detection Workflows</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>Hi,
 I'm reaching out to understand how your team currently manages incident detection and response during deployments. Lark offers a platform that focuses on continuous testing across APIs, UIs, and CLIs, which is essential for rapid incident root cause analysis. With a 99.6% test pass rate and self-healing tests, Lark minimizes disruptions during deployments, which might be particularly beneficial given your current need to maintain test efficacy in a production-critical environment.
@@ -735,51 +806,67 @@
 Best regards,</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>Interested in sharing insights on AI-driven testing solutions for incident response workflows.</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>How does your team currently manage incident detection and response during deployments?</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>Lark is an AI-driven platform providing DevOps tools for continuous testing across various surfaces including APIs, UIs, and CLIs, built by ex-Stripe engineers. It features a 99.6% test pass rate and self-healing tests that adapt to product changes, making it suitable for small engineering teams in production-critical environments.</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>• Need for rapid incident root cause analysis due to frequent deployments and updates.
 • Managing test efficacy in production-critical environments with limited SRE resources.</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small engineering teams.
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE organization.
 • Designed for small engineering teams managing production-critical systems.</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>ev_6e4143dd8364, ev_99a876d212b9, ev_b6a0d5f2bd14</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.getlark.ai/ *
+  Shows public API/integration/developer surface.
 [careers] https://docs.getlark.ai/cli *
+  Contains hiring/on-call/reliability signals.
 [fallback_page] https://docs.getlark.ai/introduction
+  Fetched from search result for additional context.
 [search_result] https://docs.getlark.ai/quickstart
+  Discovered via web search fallback.
 [search_result] https://docs.getlark.ai/secrets
+  Discovered via web search fallback.
 [homepage] https://getlark.ai *
+  Explains core product and target customer.
 [blog] https://getlark.ai/blog
+  Product updates and engineering narrative.
 [fallback_page] https://getlark.ai/terms-of-service
+  Fetched from search result for additional context.
 [search_result] https://www.getlark.ai
-[seed_metadata] https://www.ycombinator.com/companies/lark</t>
+  Discovered via web search fallback.
+[seed_metadata] https://www.ycombinator.com/companies/lark
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -810,41 +897,56 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G4" t="b">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Head of Growth or Revenue Operations</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Marcus Storm-Mollard</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Founder - CEO</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/marcus-storm-a0514aa1/</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Clarm's robust integration capabilities can streamline lead qualification and enhance the efficiency of sales operations.</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Clarm's integration capabilities are impressive for optimizing lead qualification processes.</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Exploring Inbound Conversion Challenges</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Hi Marcus,
 As the Founder and CEO at Clarm, I appreciate your focus on optimizing inbound inquiries to generate revenue. Your support and incident response capabilities indicated by the robust documentation align well with our interests. Considering the emphasis on converting inquiries effectively, I’m curious about the challenges you’ve faced in this area, particularly in managing customer interactions outside of business hours. 
@@ -852,56 +954,76 @@
 What challenges have you faced in converting inbound interest into qualified leads?</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Hi Marcus, I admire Clarm's focus on enhancing inbound conversion. I’d love to connect and discuss potential challenges in this area.</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>What challenges have you faced in converting inbound interest into qualified leads?</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Clarm is a B2B inbound automation platform that leverages AI to convert inbound inquiries into revenue, featuring REST API integration and extensive documentation for support and incident response.</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>• Converting inbound inquiries into sales effectively.
 • Managing customer interactions outside of business hours.
 • Providing rapid responses to customer inquiries to avoid drop-off.</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>• Strengthens lead qualification through advanced integration capabilities.
 • Enhances incident response with robust documentation and support.
 • Increases efficiency in managing customer interactions beyond business hours.</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>ev_dfc83857e8d7, ev_5d1ed3eb1ac1, ev_6bc561c5744c</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
         <is>
           <t>[careers] https://clarm.com/demo/careerlaunch/
+  Contains hiring/on-call/reliability signals.
 [search_result] https://clarm.com/demo/corgi/
+  Discovered via web search fallback.
 [search_result] https://clarm.com/demo/soudronic/
+  Discovered via web search fallback.
 [search_result] https://clarm.com/demo/sweep/
+  Discovered via web search fallback.
 [homepage] https://www.clarm.com *
+  Explains core product and target customer.
 [blog] https://www.clarm.com/blog *
+  Product updates and engineering narrative.
 [fallback_page] https://www.clarm.com/changelog/
+  Fetched from search result for additional context.
 [status] https://www.clarm.com/demo/
+  Indicates production uptime monitoring.
 [search_result] https://www.clarm.com/demo/verve/
+  Discovered via web search fallback.
 [docs] https://www.clarm.com/docs *
+  Shows public API/integration/developer surface.
 [fallback_page] https://www.clarm.com/pricing/
+  Fetched from search result for additional context.
 [fallback_page] https://www.clarm.com/solutions/
+  Fetched from search result for additional context.
 [fallback_page] https://www.clarm.com/tour/
-[seed_metadata] https://www.ycombinator.com/companies/clarm</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/clarm
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -932,41 +1054,52 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G5" t="b">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
         <v>1</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Head of Quality Assurance</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Shivam Agrawal</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/shivam-agrawal</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>QualGent's platform could significantly streamline your QA processes with AI-driven automation and real-time monitoring, providing faster testing and deployment.</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Exploring QA Automation Challenges</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>Hi Shivam,
 I noticed QualGent focuses on automation in mobile app testing, particularly through your AI-driven QA platform. With the increasing complexity of mobile applications and the growing reliance on CI/CD pipelines, many companies are facing challenges in enhancing their QA efficiency. 
@@ -975,51 +1108,66 @@
 Best regards,</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>Hi Shivam, I'd like to connect to discuss QA challenges and solutions in mobile app testing.</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>What are the biggest challenges you face in your current QA process?</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>QualGent is developing an AI-driven QA platform aimed at accelerating mobile app testing through automation. They provide a RESTful API that allows for effective management of mobile app testing workflows, integrating into CI/CD pipelines.</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>• Struggles with increasing the efficiency of QA processes.
 • Need for deeper integration of automated testing in CI/CD workflows.
 • Managing the testing of mobile applications across multiple devices and configurations.</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small eng teams.
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE org.
 • Fits teams that already own on-call but lack dedicated reliability headcount.</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>ev_1d337e80db61, ev_9f5f669c0ed1, ev_3b0cbe549f5c</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>[careers] https://api.qualgent.ai/ *
+  Contains hiring/on-call/reliability signals.
 [search_result] https://trust.qualgent.ai/?tab=securityControls&amp;frameworks=soc2_v1
+  Discovered via web search fallback.
 [homepage] https://www.qualgent.ai *
+  Explains core product and target customer.
 [fallback_page] https://www.qualgent.ai/about-us *
+  Fetched from search result for additional context.
 [blog] https://www.qualgent.ai/blog
+  Product updates and engineering narrative.
 [fallback_page] https://www.qualgent.ai/book-demo
+  Fetched from search result for additional context.
 [search_result] https://www.qualgent.ai/privacy-policy
+  Discovered via web search fallback.
 [fallback_page] https://www.qualgent.ai/terms-of-services
-[seed_metadata] https://www.ycombinator.com/companies/qualgent</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/qualgent
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -1050,79 +1198,110 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G6" t="b">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Security Engineer / CTO</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Are you looking to enhance your application's security posture? MindFort's tools can continuously identify and address vulnerabilities, ensuring better protection against breaches.</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>MindFort's tools enhance security by continuously identifying vulnerabilities and automating remediation.</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Exploring Continuous Security Solutions for Application Security</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>Hi, 
 I'm reaching out to discuss how companies like MindFort are addressing critical gaps in application security. Their tools enable continuous penetration testing and automate vulnerability remediation, which align with the increasing need for ongoing security assessments and fast, effective response to potential breaches. This is particularly vital for engineering teams managing limited resources while striving to maintain high security standards.
 How does MindFort prioritize vulnerability remediation in its continuous security workflow?</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>Hi, I'm exploring how MindFort enhances application security with continuous testing and automated remediation.</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>How does MindFort prioritize vulnerability remediation in its continuous security workflow?</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>MindFort is a B2B company focusing on application security, offering continuous penetration testing and vulnerability remediation tools. Recently, they secured a $3M seed funding, indicating strong market interest in their solutions, which include comprehensive API documentation and integrations suitable for small engineering teams.</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>• Need for continuous security assessment and breach response capabilities
 • Demand for quick vulnerability remediation without extensive manual work</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>• MindFort's tools enhance application security posture by continuously identifying vulnerabilities.
 • The platform automates vulnerability remediation, reducing manual intervention and saving time for engineering teams.</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>ev_b6b0cc17adb7, ev_5546a67dfea2, ev_3decd86ff312</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
         <is>
           <t>[fallback_page] https://docs.mindfort.ai
+  Fetched from search result for additional context.
 [fallback_page] https://mindfort.openstatus.dev
+  Fetched from search result for additional context.
 [status] https://status.mindfort.ai
+  Indicates production uptime monitoring.
 [homepage] https://www.mindfort.ai *
+  Explains core product and target customer.
 [fallback_page] https://www.mindfort.ai/blog
+  Fetched from search result for additional context.
 [docs] https://www.mindfort.ai/blog/seed-announcement *
+  Shows public API/integration/developer surface.
 [careers] https://www.mindfort.ai/careers *
+  Contains hiring/on-call/reliability signals.
 [fallback_page] https://www.mindfort.ai/pricing
+  Fetched from search result for additional context.
 [fallback_page] https://www.mindfort.ai/solutions/healthcare
-[seed_metadata] https://www.ycombinator.com/companies/mindfort</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/mindfort
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -1153,37 +1332,52 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G7" t="b">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
         <v>1</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Kevin Zhang</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/kevindzhang/</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Cohesive's AI-driven approach to local service business growth can dramatically enhance operational efficiencies for small engineering teams. As you are actively hiring for technical roles, I'm interested in discussing how your CRM platform can automate lead generation and client communications effectively.</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Cohesive is innovating local business growth with AI; I'd love to connect!</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Exploring Synergies between Cohesive and Emergent Delta</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>Hi Kevin,
 I noticed that Cohesive is making strides in automating local business growth through your AI-powered CRM platform. With a strong commitment to software development and active hiring in technical roles, it's clear that you are aligning well with the needs of businesses striving for effective client engagement and communication.
@@ -1191,47 +1385,58 @@
 What challenges are you currently facing in managing client communications and automating these processes?</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>Hi Kevin, I admire Cohesive's AI innovations in local business growth. Let's connect!</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>What challenges are you currently facing in managing client communications and automating these processes?</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>Cohesive focuses on automating local business growth through an AI-powered CRM platform, addressing the needs of B2B customers. They are committed to software development, as indicated by their hiring for technical roles, aligning well with Emergent Delta's focus on providing solutions in the B2B sector.</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>• Struggling to reach and engage local businesses effectively.
 • Need for a robust CRM solution that automates lead generation and follow-up.
 • Challenges in managing communications with diverse local businesses.</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="W7" s="2" t="inlineStr">
         <is>
           <t>• AI-driven growth engine tailored to local businesses.
 • Automates outreach and follow-ups, improving engagement with potential leads.
 • Integration capabilities with existing communication strategies.</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>ev_3fbd76c9297b, ev_8007205df3d3, ev_4e34f0383626</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
         <is>
           <t>[homepage] https://getcohesiveai.com *
+  Explains core product and target customer.
 [docs] https://getcohesiveai.com/api-docs *
+  Shows public API/integration/developer surface.
 [blog] https://getcohesiveai.com/blog
+  Product updates and engineering narrative.
 [careers] https://getcohesiveai.com/careers *
-[seed_metadata] https://www.ycombinator.com/companies/cohesive</t>
+  Contains hiring/on-call/reliability signals.
+[seed_metadata] https://www.ycombinator.com/companies/cohesive
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -1262,41 +1467,56 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G8" t="b">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
         <v>1</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Head of Operations or Technical Lead</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Kyle Reagan</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Co-founder and CEO</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/kyle-reagan-surfs</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Chrt aims to address the challenges in time-critical shipping, aligning with solutions that enhance operational reliability and incident management.</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Chrt is enhancing logistics for couriers and shippers with a powerful platform. Let's connect!</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Exploring Operational Challenges in Logistics</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>Hi Kyle,
 Chrt's focus on time-critical shipping is impressive, and it’s clear that maintaining operational uptime is crucial in your field. Given your emphasis on seamless logistics and integrations, I'm interested in how you currently manage incident response and root-cause analysis during shipping issues. 
@@ -1304,55 +1524,74 @@
 What challenges do you face in maintaining operational uptime during peak shipping periods?</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>Chrt is optimizing logistics for couriers and shippers. Let's connect!</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>What challenges do you face in maintaining operational uptime during peak shipping periods?</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>Chrt is a logistics platform specializing in time-critical shipping. They serve couriers, shippers, and freight forwarders by providing an integrated API to automate and enhance shipping operations.</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>• Need for faster incident response and root-cause analysis during shipping mishaps.
 • Integration with existing backend systems for logistics operations may be required.
 • Managing multiple carriers and ensuring seamless interoperability between systems.</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>• Enhanced operational reliability through faster incident resolution using AI solutions.
 • API integrations that streamline existing logistics operations and reduce manual tasks.
 • Centralized management of various carriers to improve delivery efficiency.</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>ev_0e4b2f54dcc4, ev_6ebcec500372, ev_f13ea383762d</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
         <is>
           <t>[fallback_page] https://account.chrt.com/?client_id=client_01KR50NVMGBMA0QM4D8EXKET1A&amp;redirect_uri=https%3A%2F%2Fchrt.com%2Fcallback&amp;state=Fe26.2*1*4d3fc62673d0e3ddb46a9d28781cf73b3720a9ec989e633213e25b79856a64e3*xuNufM_vZ170catrLEePlQ*yjVYxflNHV5GpNZFbTmcQ8avssjdItQDUbj9MSp1Z4q3asgV8ErhUaZHV2qsDra1AVXB030pJh6UuOJn8C_lr5yuJK0vZOm_GuA2xLQnVbweHrD7bTu4A2pj7PYs3aN9TXFIHKLAJg4QJ_3VvJrQoq7R5QmPvDJ-347z8hVqvfKplP0hFKYVkpSi2Mk0q8YI*1779155778502*9f6736e94c7605b122c13fb0aa11506729c5a320617302be56bb374c37586cc1*Vnf-ZO_AmhsZq5EaGikeChvFtxdDxqgEO19XMTjfqRQ%7E2&amp;authorization_session_id=01KRYYK5CY9Y4GVTS1KJVAFMPK
+  Fetched from search result for additional context.
 [careers] https://account.chrt.com/?client_id=client_01KR50NVMGBMA0QM4D8EXKET1A&amp;redirect_uri=https%3A%2F%2Fchrt.com%2Fcallback&amp;state=Fe26.2*1*5f817d31825fd9ec05c8428af5ac2efaa30995e481d5d63c23ed06328806d154*0rGPBr3JPfg-8FSZZ7Wy4w*fQaMsxfus7AjdUhoxVjK3VGs9Puw8oFzCq5jl-EnnJlQh4t94o7Aisv2yH3fbAZ-hLSP-WzeTIonbYSamEgMwSrL6rm-W-RFH_vmVmtOo-IJlNCQjjj9M0B7QJhcMh1vysuxRx__sqI5XU3Rxwp3zoTM05RRVQ8D4jrQ1RrOq5gwVWxq-jvWSHGTd5_3bY_Z*1779155779747*1b374d15f1b7ac5e2ef98d6bbc0487595ca4d8e5e70f46482681fce2f41ea965*DYCj3_aQDNEQCEtKRfUUsmUewKnvPXRd0uN2c1v98i0%7E2&amp;authorization_session_id=01KRYYK6K0R8XRG7KMHQN6QM4D
+  Contains hiring/on-call/reliability signals.
 [status] https://account.chrt.com/?client_id=client_01KR50NVMGBMA0QM4D8EXKET1A&amp;redirect_uri=https%3A%2F%2Fchrt.com%2Fcallback&amp;state=Fe26.2*1*82dca1eb2d7c4150a2718d7fa0d4e3fa4b47416ea296255bd74f73903f8a3699*xDuj12V24snvzSrhqJp5sQ*l2cz8VN0LGlKDmDNDz4fDWyFvI4dT_ZzsDifb-71UjxmCXGFStq45DQ21Y0auEshya7IAMJHzUaHAgcSKnZoB0fO_UxBi-bql0WOHbenaBXwReIhMrQuQCxkIo0V_LWgDnzo-I4LhtFO60qdgccxEx-vrqP-zev16FxG911MOw_OBGCa-zVVf8Q2hOXfAbCg*1779155781024*42652a3eb8bcd6c81d29ae5e0023ff5648729b3a94aeaaa2f9b00d8d629e7180*nMTHSDU20a8576aAH3nEEwQ74o6uexRVaq4CWVon51I%7E2&amp;authorization_session_id=01KRYYK7T8MF5GEPJ8KRNX7HCY
+  Indicates production uptime monitoring.
 [fallback_page] https://account.chrt.com/?client_id=client_01KR50NVMGBMA0QM4D8EXKET1A&amp;redirect_uri=https%3A%2F%2Fchrt.com%2Fcallback&amp;state=Fe26.2*1*8d85ba8fd41314f649285e6274177e32872a3bcee300c1e4991466e5cd2b1858*avJZxrxmb9vRZ3x7N2r6fQ*KMnhUblHRCwMkmnUNaaIjkoQFkVo47mlGUtDB56dVRGe4F64rXnUn5DfKTWCJ6eZRWqaMSl6QrYsgXO2ce9B-7o2URui6ysLEgUOxx-bjbjqd4j4EZk_KW4Iw2-KojlEpY3lwjJvvylh89DmSN8uwflFrSrJuG_4pVJlxzdKMl_StM0CN9fkOjU5WSSQqFpC*1779155777417*fd6e00759849d6fd0a9ade88ce16efd6fe11457e0ad7ce52d14f98999efd37c4*9SGlIXN35nfkIBuXEwJ10h4erRNYD0NHCOk8Bj98Goc%7E2&amp;authorization_session_id=01KRYYK49HQ21V64HB3608GF14
+  Fetched from search result for additional context.
 [fallback_page] https://account.chrt.com/sign-up?client_id=client_01KR50NVMGBMA0QM4D8EXKET1A&amp;redirect_uri=https%3A%2F%2Fchrt.com%2Fcallback&amp;state=Fe26.2*1*8f9f6b2f52991b53be9f8056ab22ae5c77e0069194ef9c632fcdf5063d0ceae9*r8z1uXFjMeriiyjumCG3HQ*qQJ6CnB5m9w9og3au340T4Mivi0lFvharODI-b8kr_ytckLod1x7WYQ2aBIKUDN3c-ZtMQ6h4jnI1tVCmG_DlkyOm8cdI2zJqvUWgOOu_wW3pLl-QdvUwt81_XVq8CbpTr0qM4q8ggP6H0pSf-0PaX0K2ghnPqnyx9OuQh0j2POkgERO40JpMhwV3N0SRn0w*1779155775019*3791e637eef270f1588f0854f8f078b0ed5c170745b5fdd052faae45f5ccde52*b4T1VBquhMV5aTuhR77lj893nC5_Mg9pSlnDmtg__Fs%7E2&amp;authorization_session_id=01KRYYK2AXX2VGRW7DAWR24TVC
+  Fetched from search result for additional context.
 [homepage] https://chrt.com *
+  Explains core product and target customer.
 [blog] https://chrt.com/blog
+  Product updates and engineering narrative.
 [fallback_page] https://chrt.com/pricing
+  Fetched from search result for additional context.
 [fallback_page] https://chrt.com/terms
+  Fetched from search result for additional context.
 [docs] https://docs.chrt.com/support *
+  Shows public API/integration/developer surface.
 [fallback_page] https://docs.chrt.com/welcome
+  Fetched from search result for additional context.
 [github] https://github.com/chrt-inc
-[seed_metadata] https://www.ycombinator.com/companies/chrt *</t>
+  Technical footprint and engineering culture.
+[seed_metadata] https://www.ycombinator.com/companies/chrt *
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -1383,29 +1622,36 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G9" t="b">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>CTO or Head of Engineering</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Exploring Testing Challenges for Voice AI</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>Hi,
 I noticed that Bluejay specializes in testing and monitoring voice and chat AI agents, especially in production-critical environments. Given your focus on optimizing reliability and performance, I'm curious about the challenges you face in ensuring effective monitoring and testing of your conversational AI agents. Your platform targets enterprises and startups alike, highlighting the need for robust testing before deployment.
@@ -1413,49 +1659,63 @@
 What challenges are you currently facing in monitoring and testing your conversational AI agents?</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>Hi, I'd like to connect to discuss challenges in testing and monitoring voice AI. Your insights would be valuable.</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>What challenges are you currently facing in monitoring and testing your conversational AI agents?</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>Bluejay is a testing and monitoring platform specifically designed for voice and chat AI agents, targeting enterprises and startups. It features robust API documentation and integrations, aligning with the needs of production-critical software environments.</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>• Ensuring the reliability and performance of voice AI in production environments.
 • The need for effective monitoring and testing of conversational agents before deployment.</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>• Focus on testing and monitoring voice and chat AI agents in production environments.
 • Robust API documentation and integrations for seamless software deployment.
 • Suitable for enterprises and startups looking for reliability in their AI agents.</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="X9" s="2" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>ev_df114ce00668, ev_875a01b0f68b, ev_2fb0dde8e0bd</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.getbluejay.ai/ *
+  Shows public API/integration/developer surface.
 [homepage] https://getbluejay.ai *
+  Explains core product and target customer.
 [blog] https://getbluejay.ai/blog
+  Product updates and engineering narrative.
 [fallback_page] https://getbluejay.ai/platform
+  Fetched from search result for additional context.
 [fallback_page] https://getbluejay.ai/terms-of-service
+  Fetched from search result for additional context.
 [fallback_page] https://newsletter.getbluejay.ai
+  Fetched from search result for additional context.
 [seed_metadata] https://www.ycombinator.com/companies/bluejay
-[careers] https://www.ycombinator.com/companies/bluejay/jobs</t>
+  Source list metadata (YC/CMU).
+[careers] https://www.ycombinator.com/companies/bluejay/jobs
+  Contains hiring/on-call/reliability signals.</t>
         </is>
       </c>
     </row>
@@ -1486,29 +1746,40 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G10" t="b">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>DevOps team leads or engineering managers</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Explore how Sim's AI workflows can streamline your team's incident management and help maintain uptime.</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Exploring Incident Management Solutions</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>Hi,
 I’m reaching out to discuss how Sim's open-source AI platform can enhance your incident management processes. With our robust integration capabilities, managing AI workflows becomes more efficient. Our tool can streamline root-cause analysis, aiding teams that lack dedicated reliability resources.
@@ -1517,56 +1788,76 @@
 Best regards,</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>I’d like to connect and discuss streamlining your incident management workflows with AI tools.</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>What tools does your team currently use for incident management and root cause analysis?</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>Sim is an open-source AI platform focused on building, deploying, and managing AI agents, with integrations over 1,000 tools. It supports critical production applications with strong documentation and reliable on-call support. Their solution aligns well with the Emergent Delta product, targeting small engineering teams.</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>• Need for efficient root-cause analysis in incident management
 • Integration complexities with existing tools
 • Management of AI workflows without dedicated reliability teams</t>
         </is>
       </c>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>• Faster root-cause analysis for small engineering teams
 • Hypothesis generation from logs, deploys, and runbooks without extensive SRE involvement
 • Ideal for teams that manage on-call without dedicated reliability staff</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="X10" s="2" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>ev_8afebbf91e8d, ev_058e01e6976e, ev_b27e5a16db8c</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.sim.ai *
+  Shows public API/integration/developer surface.
 [fallback_page] https://docs.sim.ai/api-reference/getting-started
+  Fetched from search result for additional context.
 [fallback_page] https://docs.sim.ai/blocks/agent
+  Fetched from search result for additional context.
 [fallback_page] https://docs.sim.ai/introduction
+  Fetched from search result for additional context.
 [fallback_page] https://docs.sim.ai/knowledgebase
+  Fetched from search result for additional context.
 [fallback_page] https://docs.sim.ai/mcp
+  Fetched from search result for additional context.
 [fallback_page] https://docs.sim.ai/self-hosting
+  Fetched from search result for additional context.
 [fallback_page] https://docs.sim.ai/tables
+  Fetched from search result for additional context.
 [github] https://github.com/simstudioai/sim
+  Technical footprint and engineering culture.
 [careers] https://jobs.ashbyhq.com/sim *
+  Contains hiring/on-call/reliability signals.
 [status] https://status.sim.ai
+  Indicates production uptime monitoring.
 [homepage] https://www.sim.ai/ *
+  Explains core product and target customer.
 [blog] https://www.sim.ai/blog
-[seed_metadata] https://www.ycombinator.com/companies/sim</t>
+  Product updates and engineering narrative.
+[seed_metadata] https://www.ycombinator.com/companies/sim
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -1597,37 +1888,52 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G11" t="b">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
         <v>1</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>Courtne Marland</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Founder/CEO</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/courtnemarland/</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Streamline your meeting workflows and enhance productivity with Lyra's solutions.</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Streamline your meeting workflows and enhance productivity with Lyra's solutions.</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Exploring Meeting Automation Challenges at Lyra</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>Hi Courtne,
 I’m reaching out to discuss potential improvements in meeting automation and communication efficiency in teams like yours at Lyra. Your platform's features such as meeting automation and CRM integration can play a critical role in facilitating these processes, especially for B2B enterprises.
@@ -1635,50 +1941,64 @@
 What challenges do you currently face in automating your meeting processes?</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>Hi Courtne, I'd like to connect to discuss meeting automation and your insights at Lyra.</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>What challenges do you currently face in automating your meeting processes?</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>Lyra is a meeting platform that automates processes and integrates with CRM systems for B2B enterprises. Known for its production-critical reliability and extensive API support, it aims to improve team communication efficiency.</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>• Need for automation in meeting processes
 • Integration challenges with CRM systems
 • Improving team communication efficiency</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>• Robust features for meeting automation and CRM integration
 • Substantial API documentation enhancing ease of integration
 • Targeted solutions for B2B enterprises looking to streamline workflows</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ev_fb3cc8b9b7e0, ev_e782e3c59422</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.lyra.so/changelog *
+  Shows public API/integration/developer surface.
 [fallback_page] https://docs.lyra.so/policies/privacy-policy
+  Fetched from search result for additional context.
 [fallback_page] https://docs.lyra.so/policies/terms-of-service
+  Fetched from search result for additional context.
 [homepage] https://lyra.so *
+  Explains core product and target customer.
 [fallback_page] https://lyra.so/pricing
+  Fetched from search result for additional context.
 [fallback_page] https://lyra.so/support
+  Fetched from search result for additional context.
 [careers] https://trylyra.notion.site/positions
-[seed_metadata] https://www.ycombinator.com/companies/lyrahq</t>
+  Contains hiring/on-call/reliability signals.
+[seed_metadata] https://www.ycombinator.com/companies/lyrahq
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -1709,37 +2029,48 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G12" t="b">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
         <v>1</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Paul Sinaï</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>CEO &amp; Co-Founder</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/paul-sinai</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Explore how Blaxel can leverage Emergent Delta to enhance incident response efficiency for their AI-capable platform.</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Incident Response Efficiency Discussion</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>Hi Paul,
 I'm reaching out to discuss Blaxel's platform for AI agents, particularly focusing on how efficient incident response is crucial for uptime and reliability. Given that your API documentation lacks explicit on-call language, I wonder if this complicates your ability to conduct thorough incident root-cause analyses. 
@@ -1749,51 +2080,68 @@
 [Your Name]</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Hi Paul, I’d like to connect to discuss incident response efficiency for Blaxel’s AI platform.</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>What challenges does Blaxel face in managing incident responses and ensuring uptime for its production platform?</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>Blaxel operates a platform for AI agents that allows for secure code execution and data sharing. It has a substantive API, but there is insufficient evidence to categorize it as production-critical.</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>• Need for efficient incident root cause analysis</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small engineering teams
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE org
 • Fits teams that already own on-call but lack dedicated reliability headcount</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="X12" s="2" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>ev_4780e323eb6c, ev_889aca15fca3, ev_b8861ddbcf60</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
         <is>
           <t>[homepage] https://blaxel.ai *
+  Explains core product and target customer.
 [blog] https://blaxel.ai/blog
+  Product updates and engineering narrative.
 [careers] https://docs.blaxel.ai/Jobs/Overview *
+  Contains hiring/on-call/reliability signals.
 [fallback_page] https://docs.blaxel.ai/Overview
+  Fetched from search result for additional context.
 [docs] https://docs.blaxel.ai/Sandboxes/Volumes *
+  Shows public API/integration/developer surface.
 [fallback_page] https://docs.blaxel.ai/changelog
+  Fetched from search result for additional context.
 [github] https://github.com/blaxel-ai
+  Technical footprint and engineering culture.
 [status] https://status.blaxel.ai
+  Indicates production uptime monitoring.
 [fallback_page] https://strapi.io
+  Fetched from search result for additional context.
 [fallback_page] https://www.sapiom.ai/
-[seed_metadata] https://www.ycombinator.com/companies/blaxel</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/blaxel
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -1824,37 +2172,44 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G13" t="b">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
         <v>1</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>Daniel Martinez</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/danielmartinezdev</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Improve Incident Response with AI Insights</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>Hi Daniel,
 I’m reaching out to discuss how TypeOS, as a B2B platform for small engineering teams, may enhance incident response processes in production-critical environments. Our AI-assisted tools focus on accelerating root-cause analysis, thereby enhancing the efficiency of your engineering workflows. The ability to maintain authorship and transparency in AI-generated content can further support your team's integrity in communications and incident handling.
@@ -1867,50 +2222,65 @@
 [Your Contact Information]</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>Hi Daniel, I’m interested in how TypeOS's AI tools enhance incident response in production teams. Let’s connect!</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>How are you currently managing incident response and root cause analysis in your engineering team?</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>TypeOS is a B2B software platform that provides AI writing tools with API integrations, tailored for small engineering teams operating in production-critical environments. Its offerings aim to facilitate faster incident root-cause analysis and maintain authorship and transparency in AI-generated content.</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>• Need for faster incident root-cause analysis in production environments
 • Maintaining authorship and transparency in AI-generated content</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small eng teams
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE org
 • Fits teams that already own on-call but lack dedicated reliability headcount</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="X13" s="2" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>ev_5d556de9e482, ev_b36ea7c0b4a6, ev_69925e10eb3b</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
         <is>
           <t>[homepage] https://typeos.com *
+  Explains core product and target customer.
 [docs] https://typeos.com/ai-detector *
+  Shows public API/integration/developer surface.
 [careers] https://typeos.com/careers *
+  Contains hiring/on-call/reliability signals.
 [changelog] https://typeos.com/changelog
+  Release discipline and operational change signals.
 [fallback_page] https://typeos.com/chatgpt-for-google-docs
+  Fetched from search result for additional context.
 [fallback_page] https://typeos.com/features
+  Fetched from search result for additional context.
 [fallback_page] https://typeos.com/pricing
+  Fetched from search result for additional context.
 [fallback_page] https://typeos.com/research
-[seed_metadata] https://www.ycombinator.com/companies/typeos</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/typeos
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -1941,41 +2311,56 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G14" t="b">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
         <v>1</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Head of Engineering</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Linus Talacko</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/linustalacko</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Consider how Den's automation capabilities can streamline your workflows and enhance incident response times without adding extra resources.</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Wondering how Den's AI automation can streamline your workflows? Let's connect.</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Exploring Task Automation Solutions for Engineering Teams</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>Hi Linus,
 I noticed Den is focused on optimizing task automation for small engineering teams through AI-powered workflows. Your ability to integrate seamlessly with various business applications could greatly enhance productivity, especially during incidents when resources are limited.
@@ -1983,47 +2368,58 @@
 What challenges do you face in managing and automating tasks across different applications?</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>Interested in how Den's AI can enhance workflows? Let's connect.</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>What challenges do you face in managing and automating tasks across different applications?</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>Den is a B2B AI-powered workspace designed to automate tasks through AI agents and integrates seamlessly with various applications using APIs and webhooks. Their comprehensive API documentation and production capabilities make them a suitable candidate for outreach regarding Emergent Delta.</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>• Need for efficient task automation in small engineering teams
 • Desire for streamlined communication between different business tools
 • Challenges in maintaining productivity during incidents due to lack of resources</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>• Enhances task automation in engineering workflows
 • Improves communication by integrating various business tools
 • Aids productivity during incidents with robust automation</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="X14" s="2" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>ev_60434ee32028, ev_b3fc3d492466, ev_b6fa47d009f0</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
         <is>
           <t>[homepage] https://getden.io *
+  Explains core product and target customer.
 [blog] https://getden.io/blog
+  Product updates and engineering narrative.
 [fallback_page] https://getden.io/pricing
+  Fetched from search result for additional context.
 [fallback_page] https://getden.io/terms
-[seed_metadata] https://www.ycombinator.com/companies/den</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/den
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -2054,37 +2450,52 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G15" t="b">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
         <v>1</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
         <is>
           <t>Lev Kokotov</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/levkk</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Engage PgDog with a focus on how Emergent Delta can enhance their incident response capabilities, particularly in multi-tenant environments where PostgreSQL sharding is crucial.</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>I admire PgDog's focus on PostgreSQL scaling. Let's connect and discuss how we might collaborate!</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Exploring PostgreSQL Scaling and Incident Management with PgDog</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>Hi Lev,
 I noticed that PgDog is focused on enhancing PostgreSQL scalability and load balancing, which aligns with the needs of businesses managing growing database demands. Your approach to providing robust solutions for horizontal scaling and incident management piqued my interest. As you work towards building a comprehensive solution geared for enterprise use, I believe insights from Emergent Delta's AI-assisted incident root-cause analysis could complement your goals, especially in multi-tenant environments where PostgreSQL sharding is critical.
@@ -2093,53 +2504,70 @@
 [Your Name]</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>Hi Lev, I see PgDog's focus on PostgreSQL scaling solutions. Let's connect to discuss potential synergies!</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>What are the current challenges you face while managing your PostgreSQL instances, particularly in scaling and incident response?</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>PgDog provides solutions for horizontal scaling and load balancing for PostgreSQL databases, targeting software needs for B2B applications. Their documentation and hiring signals indicate a robust solution for enterprise use.</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>• Need for enhanced PostgreSQL scaling solutions
 • Challenges in managing growing database loads
 • Desire for integrated tooling for incident management</t>
         </is>
       </c>
-      <c r="T15" s="2" t="inlineStr">
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small eng teams
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE org
 • Fits teams that already own on-call but lack dedicated reliability headcount</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="X15" s="2" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>ev_d50bb7ac1376, ev_f0141f86cf5f, ev_b03414a14ef0</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.pgdog.dev *
+  Shows public API/integration/developer surface.
 [fallback_page] https://docs.pgdog.dev/features/load-balancer/
+  Fetched from search result for additional context.
 [fallback_page] https://docs.pgdog.dev/features/sharding/
+  Fetched from search result for additional context.
 [fallback_page] https://docs.pgdog.dev/features/transaction-mode/
+  Fetched from search result for additional context.
 [fallback_page] https://docs.pgdog.dev/installation/
+  Fetched from search result for additional context.
 [github] https://github.com/pgdogdev/pgdog
+  Technical footprint and engineering culture.
 [homepage] https://pgdog.dev *
+  Explains core product and target customer.
 [blog] https://pgdog.dev/blog/
+  Product updates and engineering narrative.
 [careers] https://pgdog.dev/careers *
+  Contains hiring/on-call/reliability signals.
 [status] https://pgdog.dev/status
-[seed_metadata] https://www.ycombinator.com/companies/pgdog</t>
+  Indicates production uptime monitoring.
+[seed_metadata] https://www.ycombinator.com/companies/pgdog
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -2170,37 +2598,44 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G16" t="b">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
         <v>1</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
         <is>
           <t>Raman Varma</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/ramanvarma/</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Inquiry About Cloud Incident Management Solutions</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>Hi Raman,
 I came across Kestrel AI and noticed your emphasis on AI-powered incident response for cloud services and Kubernetes management. Your platform's capabilities to automatically identify and remediate cloud and Kubernetes incidents are particularly intriguing given the increasing complexity in cloud environments today.
@@ -2210,50 +2645,64 @@
 [Your Name]</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>Hi Raman, I'm impressed by Kestrel AI's AI-driven incident response solutions. I'd love to connect and learn more about your work.</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>What strategies have you found most effective in addressing the challenge of automated root cause analysis?</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>Kestrel AI is a B2B-focused incident response platform that offers AI-powered solutions for cloud incidents and Kubernetes management, with substantial operational capabilities and a focus on integration with cloud services.</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>• Managing cloud and Kubernetes incidents
 • Automating root cause analysis
 • Identifying cross-domain security risks</t>
         </is>
       </c>
-      <c r="T16" s="2" t="inlineStr">
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>• AI-powered solutions to streamline incident management
 • Integration capabilities with existing cloud services
 • Focus on operational efficiency for engineering teams</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="X16" s="2" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>ev_87643c070ff3, ev_08b72001e727, ev_482a4ecc4d1e</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
         <is>
           <t>[fallback_page] https://docs.usekestrel.ai/introduction
+  Fetched from search result for additional context.
 [docs] https://docs.usekestrel.ai/quickstart *
+  Shows public API/integration/developer surface.
 [github] https://github.com/KestrelAI/Kestrel-Operator
+  Technical footprint and engineering culture.
 [status] https://status.usekestrel.ai
+  Indicates production uptime monitoring.
 [homepage] https://usekestrel.ai *
+  Explains core product and target customer.
 [fallback_page] https://usekestrel.ai/blog
+  Fetched from search result for additional context.
 [changelog] https://usekestrel.ai/changelog
-[seed_metadata] https://www.ycombinator.com/companies/kestrel-ai</t>
+  Release discipline and operational change signals.
+[seed_metadata] https://www.ycombinator.com/companies/kestrel-ai
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -2284,29 +2733,44 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G17" t="b">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>CTO or Head of Engineering</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Explore how Hyperspell can enhance the memory capabilities of your AI agents and improve incident response with AI-assisted analytics.</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Let's connect on AI memory and context for agents.</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Exploring AI Memory Integration Challenges</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>Hi, 
 I am reaching out because Hyperspell specializes in enhancing the memory and context capabilities of AI agents, which aligns with trends in B2B applications where production reliability is crucial. Our platform addresses common challenges such as integrating diverse data sources for AI-driven interfaces and improving incident response through AI-assisted analytics.
@@ -2314,48 +2778,61 @@
 Best regards,</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>I'm interested in discussing AI memory integration challenges at your company.</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>What challenges do you face in integrating and managing data sources for your AI agents?</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>Hyperspell is a B2B software platform focused on providing memory and context for AI agents. It offers integrations, webhooks, and aims to support B2B use cases, particularly where production reliability is critical.</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>• Need for improved incident response and root cause analysis in production systems.
 • Challenges with integrating various data sources for AI-driven interfaces.</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small eng teams
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE org
 • Fits teams that already own on-call but lack dedicated reliability headcount</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="X17" s="2" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>ev_079356616f85, ev_3547289ba72a, ev_7652f5090e59</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.hyperspell.com *
+  Shows public API/integration/developer surface.
 [fallback_page] https://docs.hyperspell.com/core/introduction
+  Fetched from search result for additional context.
 [github] https://github.com/hyperspell
+  Technical footprint and engineering culture.
 [search_result] https://hyperspell.com/
+  Discovered via web search fallback.
 [homepage] https://www.hyperspell.com/ *
+  Explains core product and target customer.
 [blog] https://www.hyperspell.com/blog
-[seed_metadata] https://www.ycombinator.com/companies/hyperspell</t>
+  Product updates and engineering narrative.
+[seed_metadata] https://www.ycombinator.com/companies/hyperspell
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -2386,29 +2863,40 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G18" t="b">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>CTO or Head of Engineering</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Metorial's API and integrations can help streamline your incident response and improve operational efficiency within your engineering team.</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Exploring Integration Solutions for Incident Management</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>Hello,
 Metorial provides a robust infrastructure for AI-native companies, enabling seamless integration and connection of tools for engineering teams. I noticed that your team might be dealing with integration complexities and operational support challenges without a full SRE organization. Our product, Emergent Delta, is designed to assist small engineering teams in conducting efficient incident root-cause analysis, even those without a dedicated reliability headcount.
@@ -2418,55 +2906,74 @@
 [Your Name]</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>Hi! I’m interested in how Metorial's infrastructure supports AI-native companies like yours.</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>How do you currently manage incident analysis and response within your engineering teams?</t>
         </is>
       </c>
-      <c r="R18" s="2" t="inlineStr">
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>Metorial provides infrastructure for AI-native companies, integrating tools and skills effectively. It aligns with the operational needs of engineering teams, offering strong API documentation and integrations that support B2B software teams.</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>• Need for efficient incident root-cause analysis in a small team setting.
 • Integration complexities that require robust tooling.
 • Operational support without a full SRE organization.</t>
         </is>
       </c>
-      <c r="T18" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small eng teams
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE org
 • Fits teams that already own on-call but lack dedicated reliability headcount</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>ev_84e7406b535b, ev_af82d1b78eac, ev_f318d3d43d95</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>[github] https://github.com/metorial
+  Technical footprint and engineering culture.
 [fallback_page] https://github.com/metorial/metorial-node
+  Fetched from search result for additional context.
 [fallback_page] https://github.com/metorial/metorial-python
+  Fetched from search result for additional context.
 [fallback_page] https://marketplace.metorial.com/providers
+  Fetched from search result for additional context.
 [docs] https://marketplace.metorial.com/providers?search=Apify
+  Shows public API/integration/developer surface.
 [careers] https://meteor.computer/careers *
+  Contains hiring/on-call/reliability signals.
 [homepage] https://metorial.com *
+  Explains core product and target customer.
 [fallback_page] https://metorial.com/api
+  Fetched from search result for additional context.
 [blog] https://metorial.com/blog
+  Product updates and engineering narrative.
 [fallback_page] https://metorial.com/docs *
+  Fetched from search result for additional context.
 [fallback_page] https://metorial.com/legal/api-terms
+  Fetched from search result for additional context.
 [status] https://status.metorial.com
-[seed_metadata] https://www.ycombinator.com/companies/metorial</t>
+  Indicates production uptime monitoring.
+[seed_metadata] https://www.ycombinator.com/companies/metorial
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -2497,37 +3004,52 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G19" t="b">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
         <v>1</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t>Shikhar Bhushan</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Co-founder and CEO</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/shikhrr</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>S2.dev's focus on real-time data streams could greatly benefit from Emergent Delta's incident RCA insights tailored for small engineering teams.</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>S2.dev's focus on real-time data streams could benefit from our RCA insights. Let's connect!</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Exploring RCA for Your Real-Time Data Streams</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>Hi Shikhar,
 I came across S2.dev and your innovative approach to durable streaming APIs for real-time data applications. Given your focus on production-critical software, I believe there’s alignment with Emergent Delta’s capabilities in providing AI-assisted root-cause analysis (RCA) tailored for small engineering teams. 
@@ -2537,59 +3059,82 @@
 [Your Name]</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>Hi Shikhar, I'm interested in connecting to discuss RCA insights for real-time streaming applications.</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>How does your team currently handle incident management and root cause analysis for your real-time streaming applications?</t>
         </is>
       </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>S2.dev offers a durable streaming API designed for production-critical software, backed by Y Combinator. Their focus is on real-time data infrastructure, ideal for small engineering teams.</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>• Need for effective root-cause analysis tools without dedicated SRE teams
 • Challenges of managing real-time data streams
 • Scaling backend infrastructure for streaming applications</t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr">
+      <c r="W19" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small eng teams
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE org
 • Fits teams that already own on-call but lack dedicated reliability headcount</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" s="2" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>ev_63b179fc0494, ev_c3f3a8099191, ev_d6a4122d552a, ev_c8de830f410c</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
         <is>
           <t>[fallback_page] https://github.com/s2-streamstore
+  Fetched from search result for additional context.
 [fallback_page] https://github.com/s2-streamstore/s2
+  Fetched from search result for additional context.
 [homepage] https://s2.dev *
+  Explains core product and target customer.
 [fallback_page] https://s2.dev/blog
+  Fetched from search result for additional context.
 [search_result] https://s2.dev/blog/access-control
+  Discovered via web search fallback.
 [blog] https://s2.dev/blog/ga *
+  Product updates and engineering narrative.
 [fallback_page] https://s2.dev/blog/intro
+  Fetched from search result for additional context.
 [search_result] https://s2.dev/blog/video-conferencing
+  Discovered via web search fallback.
 [search_result] https://s2.dev/careers
+  Discovered via web search fallback.
 [docs] https://s2.dev/docs
+  Shows public API/integration/developer surface.
 [fallback_page] https://s2.dev/docs/concepts/reads#consistency
+  Fetched from search result for additional context.
 [search_result] https://s2.dev/docs/integrations/flink *
+  Discovered via web search fallback.
 [fallback_page] https://s2.dev/docs/intro *
+  Fetched from search result for additional context.
 [search_result] https://s2.dev/docs/platform/architecture
+  Discovered via web search fallback.
 [careers] https://s2.dev/docs/use-cases/live-view
+  Contains hiring/on-call/reliability signals.
 [status] https://status.s2.dev
-[seed_metadata] https://www.ycombinator.com/companies/s2-dev</t>
+  Indicates production uptime monitoring.
+[seed_metadata] https://www.ycombinator.com/companies/s2-dev
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -2620,29 +3165,44 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G20" t="b">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>DevOps Manager or Engineering Lead</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Empowering your small engineering team with AI to handle on-call responsibilities without the burnout.</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Empowering your small engineering team to handle on-call responsibilities without the burnout.</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Exploring Incident Management Challenges</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>Hello,
 At Deeptrace, we provide an AI-assisted incident root-cause analysis tool designed to empower small engineering teams like yours, particularly where SRE resources are limited. Our platform integrates seamlessly into existing structures to help streamline incident management and support faster resolution times, while aiming to reduce alert fatigue commonly experienced by your team.
@@ -2653,50 +3213,64 @@
 [Your Company]</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>Hi, I’d like to connect and discuss how small engineering teams manage production incidents.</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>What challenges do you face in managing production alerts and incidents?</t>
         </is>
       </c>
-      <c r="R20" s="2" t="inlineStr">
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>Deeptrace offers an incident root-cause analysis tool aimed specifically at small engineering teams, enhancing their incident management capabilities and reducing downtime.</t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>• Need for faster incident resolution
 • Reduction of alert fatigue
 • Difficulty in managing production incidents with limited on-call resources</t>
         </is>
       </c>
-      <c r="T20" s="2" t="inlineStr">
+      <c r="W20" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small eng teams
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE org
 • Fits teams that already own on-call but lack dedicated reliability headcount</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" s="2" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>ev_4ac84da66ad2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>[homepage] https://deeptrace.com
+  Explains core product and target customer.
 [blog] https://deeptrace.com/blog
+  Product updates and engineering narrative.
 [fallback_page] https://deeptrace.com/terms-of-service
+  Fetched from search result for additional context.
 [docs] https://docs.deeptrace.com/introduction *
+  Shows public API/integration/developer surface.
 [careers] https://jobs.ashbyhq.com/bluerocksecurity/f028b16f-f308-4343-96f6-d86fec16a8ee
+  Contains hiring/on-call/reliability signals.
 [status] https://status.deeptrace.com
+  Indicates production uptime monitoring.
 [fallback_page] https://trust.deeptrace.com/controls
-[seed_metadata] https://www.ycombinator.com/companies/deeptrace</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/deeptrace
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -2727,29 +3301,44 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G21" t="b">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>CTO or Head of Engineering focusing on AI or unstructured data solutions</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Explore how Unsiloed AI can enhance your document processing workflows by turning complex multimodal documents into structured and actionable insights for your teams.</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Interested in understanding how AI can transform unstructured data workflows in your enterprise.</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Inquiry on Unstructured Data Processing Solutions</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>Dear CTO or Head of Engineering,
 I’m reaching out regarding Unsiloed AI and its innovative API for parsing multimodal unstructured data. As organizations increasingly rely on efficient data processing workflows, handling complexities within documents becomes critical. Your API seems well-positioned to tackle these challenges, especially considering its focus on enterprise applications.
@@ -2758,53 +3347,70 @@
 [Your Name]</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>Interested in discussing unstructured data solutions and collaboration opportunities.</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>What challenges do you face with unstructured data processing in your current systems?</t>
         </is>
       </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>Unsiloed AI is developing an API for parsing multimodal unstructured data, targeted at enterprise applications. They provide documentation for their API and are positioned within the B2B technology sector, making them a strong candidate for potential collaboration and discovery.</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>• Reliance on accurate parsing of unstructured data for business operations
 • Need for seamless extraction of information from complex documents used within enterprises
 • Demands for AI integration that requires reliable incident response capability</t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>• Enhances accuracy in parsing unstructured data, crucial for business operations
 • Facilitates seamless extraction from complex enterprise documents
 • Supports AI integration with robust incident response capabilities</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" s="2" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>ev_36de5d16e9d9</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.unsiloed.ai/
+  Shows public API/integration/developer surface.
 [github] https://github.com/Unsiloed-AI
+  Technical footprint and engineering culture.
 [careers] https://jobs.gem.com/unsiloed-ai *
+  Contains hiring/on-call/reliability signals.
 [homepage] https://www.unsiloed.ai
+  Explains core product and target customer.
 [fallback_page] https://www.unsiloed.ai/about
+  Fetched from search result for additional context.
 [fallback_page] https://www.unsiloed.ai/about-us
+  Fetched from search result for additional context.
 [blog] https://www.unsiloed.ai/blog
+  Product updates and engineering narrative.
 [fallback_page] https://www.unsiloed.ai/pricing
+  Fetched from search result for additional context.
 [status] https://www.unsiloed.ai/status
+  Indicates production uptime monitoring.
 [fallback_page] https://www.unsiloed.ai/team
-[seed_metadata] https://www.ycombinator.com/companies/unsiloed-ai</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/unsiloed-ai
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -2835,29 +3441,44 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G22" t="b">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H22" t="b">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>CTO or Head of Engineering at mid-sized B2B companies</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Bolna AI's multilingual voice agents can streamline customer interactions for your diverse user base, ensuring efficient handling of calls across various languages.</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Exploring multilingual support solutions for effective customer interactions at Bolna AI.</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Exploring Multilingual Voice AI Solutions</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>Hello,
 I am reaching out to discuss Bolna AI's voice AI platform, which provides a robust multilingual voice agent solution that can enhance your customer interactions. Our platform is designed to support enterprises by improving scalability in managing inbound and outbound communications, particularly in a multilingual context.
@@ -2865,54 +3486,72 @@
 I would like to understand more about the specific issues you encounter regarding scalability and integration of voice technology. What challenges are you currently facing with your customer support call operations?</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>Exploring multilingual support solutions for effective customer interactions at Bolna AI.</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>What challenges are you currently facing with your customer support call operations?</t>
         </is>
       </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>Bolna AI offers a voice AI platform tailored for enterprises, focusing on multilingual capabilities and scalability for inbound and outbound communications. The company provides a multilingual voice agent solution, which can improve customer satisfaction by efficiently handling calls in various languages.</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>• Need for multilingual support in customer interactions
 • Scalability issues with managing voice calls or agents
 • Challenges in integrating voice AI with existing systems</t>
         </is>
       </c>
-      <c r="T22" s="2" t="inlineStr">
+      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>• Enhances customer satisfaction through effective multilingual communication
 • Improves scalability in managing inbound and outbound voice interactions
 • Provides seamless integration with existing systems for voice AI</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" s="2" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
         <is>
           <t>no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>ev_81ccd484009d, ev_d1e6f9ef829e, ev_ec7a1155e606</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
         <is>
           <t>[status] https://status.bolna.ai
+  Indicates production uptime monitoring.
 [homepage] https://www.bolna.ai/ *
+  Explains core product and target customer.
 [careers] https://www.bolna.ai/careers *
+  Contains hiring/on-call/reliability signals.
 [docs] https://www.bolna.ai/docs *
+  Shows public API/integration/developer surface.
 [fallback_page] https://www.bolna.ai/docs/api-reference/agent/v2/overview
+  Fetched from search result for additional context.
 [fallback_page] https://www.bolna.ai/docs/api-reference/calls/overview
+  Fetched from search result for additional context.
 [fallback_page] https://www.bolna.ai/docs/api-reference/executions/overview
+  Fetched from search result for additional context.
 [fallback_page] https://www.bolna.ai/docs/api-reference/inbound/overview
+  Fetched from search result for additional context.
 [fallback_page] https://www.bolna.ai/docs/api-reference/introduction
+  Fetched from search result for additional context.
 [fallback_page] https://www.bolna.ai/docs/api-reference/phone-numbers/overview
+  Fetched from search result for additional context.
 [blog] https://www.bolna.ai/newsroom/bolna-bags-63-million-seed-funding-led-by-general-catalyst-to-build-indias-voice-ai-platform
-[seed_metadata] https://www.ycombinator.com/companies/bolna-ai</t>
+  Product updates and engineering narrative.
+[seed_metadata] https://www.ycombinator.com/companies/bolna-ai
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -2943,80 +3582,111 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G23" t="b">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H23" t="b">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>CTO or Lead Engineer at a B2B software firm</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>Explore how Lua's developer-friendly environment can enhance the incident response capabilities of your engineering team.</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>Lua helps small engineering teams rapidly analyze incidents with AI agents.</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Streamlining Incident Management for Engineering Teams</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>Hello,
 At Lua Global Inc, we focus on enabling the development of AI agents tailored for production-critical environments. Our platform is designed for small engineering teams that may need support in incident management and root-cause analysis. With our APIs and developer-friendly documentation, you can rapidly deploy solutions that help surface insights from logs and runbooks without the necessity of a full SRE team.
 I'm curious about how your team currently handles incident management and root-cause analysis. Would you be open to discussing your processes further?</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>Lua helps small engineering teams rapidly analyze incidents with AI agents.</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>How currently do you handle incident management and root-cause analysis?</t>
         </is>
       </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>Lua Global Inc is a B2B platform that enables the development of AI agents with a focus on production-critical environments. They provide API documentation and integrations, making them suitable for engineering teams seeking enhanced incident response capabilities.</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>• Need for rapid incident root-cause analysis
 • Support for small engineering teams lacking dedicated SRE resources</t>
         </is>
       </c>
-      <c r="T23" s="2" t="inlineStr">
+      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small engineering teams
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE organization
 • Fits teams that already own on-call but lack dedicated reliability headcount</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" s="2" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>ev_e8a5014b29f1, ev_12ae57005a8f, ev_72a3eff000dd</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
         <is>
           <t>[blog] https://blog.heylua.ai/
+  Product updates and engineering narrative.
 [fallback_page] https://docs.heylua.ai
+  Fetched from search result for additional context.
 [fallback_page] https://docs.heylua.ai/api/overview
+  Fetched from search result for additional context.
 [fallback_page] https://docs.heylua.ai/examples/overview
+  Fetched from search result for additional context.
 [homepage] https://heylua.ai *
+  Explains core product and target customer.
 [careers] https://heylua.ai/careers *
+  Contains hiring/on-call/reliability signals.
 [docs] https://heylua.ai/developers/ *
+  Shows public API/integration/developer surface.
 [fallback_page] https://heylua.ai/templates
+  Fetched from search result for additional context.
 [fallback_page] https://heylua.ai/terms-of-service
-[seed_metadata] https://www.ycombinator.com/companies/lua-global-inc</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/lua-global-inc
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -3047,29 +3717,44 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G24" t="b">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H24" t="b">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>CTO or Head of Engineering</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Leverage VideoGen's API to enhance your video editing workflows and improve turnaround time for your marketing team.</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Looking to discuss how VideoGen enhances video production efficiency with its API.</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Exploring Video Production Scalability Challenges</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>Hello,
 I came across VideoGen’s AI video generation platform, particularly its ability to automate video creation and editing through your API. Given its emphasis on efficient video production and reliability, it seems to resonate well with the challenges many organizations face today in scaling video content effectively.
@@ -3078,53 +3763,70 @@
 Thank you for your time.</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>Hi, I see that VideoGen focuses on AI for video generation. I'd like to connect and discuss how your team scales video production.</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>What challenges do you currently face in scaling your video production processes?</t>
         </is>
       </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>VideoGen is an AI video generation platform that enables users to create and edit professional videos through an automation-friendly API, showcasing a commitment to customer support and reliability.</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>• Need to scale video production efficiently
 • Integration challenges for existing tools
 • Time-consuming video editing processes</t>
         </is>
       </c>
-      <c r="T24" s="2" t="inlineStr">
+      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>• Streamlined video creation and editing through automation
 • Improved scalability for video production efforts
 • User-friendly API integrations for existing workflows</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" s="2" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>ev_863038584496, ev_974fcbdb8c0f</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
         <is>
           <t>[careers] https://app.dover.com/jobs/videogen *
+  Contains hiring/on-call/reliability signals.
 [blog] https://blog.videogen.io
+  Product updates and engineering narrative.
 [fallback_page] https://docs.videogen.io/introduction
+  Fetched from search result for additional context.
 [status] https://status.videogen.io
+  Indicates production uptime monitoring.
 [homepage] https://videogen.io
+  Explains core product and target customer.
 [fallback_page] https://videogen.io/changelog
+  Fetched from search result for additional context.
 [fallback_page] https://videogen.io/news
+  Fetched from search result for additional context.
 [fallback_page] https://videogen.io/pricing
+  Fetched from search result for additional context.
 [fallback_page] https://videogen.io/solutions
+  Fetched from search result for additional context.
 [docs] https://videogen.io/videogen-api *
-[seed_metadata] https://www.ycombinator.com/companies/videogen</t>
+  Shows public API/integration/developer surface.
+[seed_metadata] https://www.ycombinator.com/companies/videogen
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -3155,41 +3857,56 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G25" t="b">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H25" t="b">
         <v>1</v>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Technical lead or Engineering Manager</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Sean Roades</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/sr19943/</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>Consider how Emergent Delta could enhance your operational reliability by leveraging your existing messaging API for rapid incident root-cause analysis. We specialize in aiding teams with efficient systems to uncover issues swiftly.</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Let's connect! I'm interested in how your messaging API can streamline incident resolution.</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Understanding Your Messaging Integration Challenges</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>Hi Sean,
 I noticed that Pinnacle focuses on providing a messaging API for B2B applications, which is key for efficient communication within teams. Given the importance of integrating multiple messaging formats like SMS, MMS, and RCS, I’m curious about the challenges you face in managing these integrations effectively.
@@ -3197,51 +3914,66 @@
 What challenges do you face regarding the integration and management of your messaging services?</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>Interested in how Pinnacle is enhancing messaging APIs for better incident management.</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>What challenges do you face regarding the integration and management of your messaging services?</t>
         </is>
       </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t>Pinnacle provides a messaging API that enables developers to integrate various messaging formats like SMS, MMS, and RCS, focusing on B2B applications with features such as API integrations, webhooks, and status monitoring suitable for production-critical use cases.</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>• Need for efficient messaging integration into applications
 • Requirement for reliable messaging services with status monitoring
 • Challenges in managing multiple messaging formats (SMS, MMS, RCS)</t>
         </is>
       </c>
-      <c r="T25" s="2" t="inlineStr">
+      <c r="W25" s="2" t="inlineStr">
         <is>
           <t>• Consolidation of messaging formats through a single API interface
 • Enhanced visibility and monitoring for messaging services
 • Support for rapid integration to optimize deployment cycles</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" s="2" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>homepage, docs</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.pinnacle.sh/api-reference/messages/send-mms
+  Shows public API/integration/developer surface.
 [fallback_page] https://docs.pinnacle.sh/mcp/mcp-server
+  Fetched from search result for additional context.
 [search_result] https://pinnacle.sh/blog/rcs-typing-indicators-real-time-user-status
+  Discovered via web search fallback.
 [status] https://status.pinnacle.sh
+  Indicates production uptime monitoring.
 [homepage] https://www.pinnacle.sh/
+  Explains core product and target customer.
 [blog] https://www.pinnacle.sh/blog
+  Product updates and engineering narrative.
 [search_result] https://www.pinnacle.sh/blog/rcs-analytics-the-business-leverage-behind-rich-messaging
+  Discovered via web search fallback.
 [careers] https://www.pinnacle.sh/blog/sms-api-integrate-messaging-into-your-application
-[seed_metadata] https://www.ycombinator.com/companies/pinnacle</t>
+  Contains hiring/on-call/reliability signals.
+[seed_metadata] https://www.ycombinator.com/companies/pinnacle
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -3272,29 +4004,44 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G26" t="b">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H26" t="b">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>CTO or Head of Engineering</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>Enhance your incident response capabilities with AI-assisted RCA that fits your engineering team's size and needs.</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>Maximize incident response effectiveness with AI-driven RCA, tailored for smaller teams.</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Exploring Incident Response Challenges</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>Hello,
 I’m reaching out to discuss the incident resolution processes your team utilizes for managing robotic stations at Autumn Labs. Given your focus on streamlining operations with a small production team, I believe there's significant potential to leverage AI for faster root-cause analysis and incident management without the extensive infrastructure typically seen in larger enterprises.
@@ -3302,46 +4049,57 @@
 What challenges do you face in managing incident responses and root-cause analyses with your current team structure?</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>Interested in discussing incident response strategies for small production teams focused on efficiency.</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>What challenges do you face in managing incident responses and root-cause analyses with your current team structure?</t>
         </is>
       </c>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="U26" s="2" t="inlineStr">
         <is>
           <t>Autumn Labs offers an AI-driven platform specializing in monitoring and managing robotic stations, aiding small production teams primarily in root-cause analysis. Their approach aims to enhance operational efficiency in manufacturing through real-time insights and analytics.</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>• Need for accelerated incident resolution processes due to small team size.
 • Lack of robust support structures compared to larger enterprises with dedicated SRE teams.</t>
         </is>
       </c>
-      <c r="T26" s="2" t="inlineStr">
+      <c r="W26" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis tailored for small engineering teams. 
 • Expertise in surfacing actionable insights from logs and production data without a full SRE organization.
 • Designed to support teams with existing on-call structures but limited reliability headcount.</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" s="2" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>ev_dbd548357334, ev_54d780fe8f34, ev_2ca66ae7a632</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
         <is>
           <t>[homepage] https://autumnlabs.io/ *
+  Explains core product and target customer.
 [blog] https://autumnlabs.io/blog
+  Product updates and engineering narrative.
 [careers] https://autumnlabs.io/careers *
+  Contains hiring/on-call/reliability signals.
 [docs] https://autumnlabs.io/docs *
-[seed_metadata] https://www.ycombinator.com/companies/autumn-labs</t>
+  Shows public API/integration/developer surface.
+[seed_metadata] https://www.ycombinator.com/companies/autumn-labs
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -3372,41 +4130,56 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G27" t="b">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H27" t="b">
         <v>1</v>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Head of Engineering or API Product Manager</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Shreya Karpoor</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/shreya-karpoor</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>Explore how Simplex's API can streamline provider enrollment processes for your platform, ensuring faster and more reliable integrations with payors.</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>Interested in how Simplex's API can optimize provider enrollment? Let's connect!</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Streamline Provider Enrollment Processes with Simplex API</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>Hi Shreya,
 I came across Simplex and the API you offer for automating provider enrollment in healthcare. It appears particularly well-suited for improving workflows by enhancing automation and providing real-time updates on enrollment statuses.
@@ -3419,54 +4192,72 @@
 [Your Contact Information]</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
         <is>
           <t>Hi Shreya, I'd love to connect and discuss how Simplex's API can enhance provider enrollment workflows in healthcare.</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>What challenges do you face with your current provider enrollment processes?</t>
         </is>
       </c>
-      <c r="R27" s="2" t="inlineStr">
+      <c r="U27" s="2" t="inlineStr">
         <is>
           <t>Simplex provides an API for automating provider enrollment, appealing to B2B sectors, particularly within healthcare. The presence of on-call language and substantive API documentation strengthens its fit for outreach.</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>• Streamlining provider enrollment processes with payers
 • Enhancing automation in healthcare workflows
 • Ensuring real-time updates on enrollment statuses</t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
+      <c r="W27" s="2" t="inlineStr">
         <is>
           <t>• Automates provider enrollment, reducing manual effort
 • Ensures faster and more reliable integrations with payers
 • Provides real-time tracking of enrollment statuses</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" s="2" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>ev_e9cd7decb8fd, ev_6413143ca676, ev_3bd7ceb07169</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
         <is>
           <t>[docs] https://simplex.sh/docs *
+  Shows public API/integration/developer surface.
 [search_result] https://simplex.sh/docs/integrating-simplex/webhooks
+  Discovered via web search fallback.
 [homepage] https://www.simplex.sh/ *
+  Explains core product and target customer.
 [blog] https://www.simplex.sh/blog
+  Product updates and engineering narrative.
 [fallback_page] https://www.simplex.sh/changelog
+  Fetched from search result for additional context.
 [careers] https://www.simplex.sh/docs/integrating-simplex/webhooks
+  Contains hiring/on-call/reliability signals.
 [fallback_page] https://www.simplex.sh/docs/prior-auth-sdk/overview
+  Fetched from search result for additional context.
 [search_result] https://www.simplex.sh/privacy-policy
+  Discovered via web search fallback.
 [status] https://www.simplex.sh/status *
+  Indicates production uptime monitoring.
 [fallback_page] https://www.simplex.sh/support
+  Fetched from search result for additional context.
 [fallback_page] https://www.simplex.sh/terms-of-service
-[seed_metadata] https://www.ycombinator.com/companies/simplex</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/simplex
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -3497,29 +4288,44 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G28" t="b">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H28" t="b">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>CTO or Head of Engineering</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>Decisional AI simplifies the development and deployment of AI agents for your workflows.</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Decisional AI builds AI agents to automate business workflows efficiently.</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Exploring Automation Solutions for Your Workflows</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>Hello,
 At Decisional AI, we specialize in building AI agents designed to automate workflows for small production teams, particularly in B2B contexts. Our offerings are rooted in solid API documentation, facilitating the management of multiple integrations and easing the setup of AI agents.
@@ -3528,56 +4334,76 @@
 Looking forward to your insights.</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>Hi, I'd like to connect and discuss your current workflow management and automation challenges.</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>How are you currently managing your workflows and what challenges do you face with automation?</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>Decisional AI builds AI agents for automating workflows with a B2B focus and solid API documentation, aligning with the ideal customer profile of enterprise solutions targeting small production teams.</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>• Need for automation in repetitive workflows
 • Challenges managing multiple integrations efficiently
 • Desire for ease of use in setting up AI agents</t>
         </is>
       </c>
-      <c r="T28" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>• Facilitates efficient automation of workflows
 • Streamlines integration management across tools
 • Simplifies setup of AI agents, enhancing user experience</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>ev_2337068cd67a, ev_ff94f397fa51, ev_b0744fcce1b9</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.decisional.com/ *
+  Shows public API/integration/developer surface.
 [fallback_page] https://docs.decisional.com/introduction *
+  Fetched from search result for additional context.
 [search_result] https://finance.decisional.com/
+  Discovered via web search fallback.
 [careers] https://finance.decisional.com/about
+  Contains hiring/on-call/reliability signals.
 [search_result] https://finance.decisional.com/privacy-policy
+  Discovered via web search fallback.
 [search_result] https://finance.decisional.com/toc
+  Discovered via web search fallback.
 [status] https://status.decisional.com
+  Indicates production uptime monitoring.
 [homepage] https://www.decisional.com *
+  Explains core product and target customer.
 [blog] https://www.decisional.com/blog
+  Product updates and engineering narrative.
 [fallback_page] https://www.decisional.com/blog/decisional-vs-n8n
+  Fetched from search result for additional context.
 [fallback_page] https://www.decisional.com/blog/decisional-vs-zapier-agents
+  Fetched from search result for additional context.
 [fallback_page] https://www.decisional.com/changelog
+  Fetched from search result for additional context.
 [fallback_page] https://www.decisional.com/pricing
-[seed_metadata] https://www.ycombinator.com/companies/decisional-ai</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/decisional-ai
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -3608,29 +4434,40 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G29" t="b">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H29" t="b">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>CTO or engineering lead</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>Thunder Compute’s focus on developer-friendly GPU services can benefit from enhanced incident response capabilities through Emergent Delta, pending further alignment on specific services offered.</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Exploring Incident Response Strategies</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>Hello,
 Thunder Compute has a strong foundation in providing cloud-based GPU resources tailored for developers and production-critical software teams. As you look to support your client base with faster incident resolution, developing streamlined incident response systems can be crucial amidst rapid deployment cycles.
@@ -3639,50 +4476,65 @@
 Best regards,</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>Hi! I see Thunder Compute provides GPU resources for development teams. Interested to connect &amp; learn more.</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>How are you currently managing your incident responses and reliability as your service scales?</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>Thunder Compute is a startup offering a cloud service focused on providing GPU resources. They cater to developers and production-critical software teams, having both documentation and operational proof of their services.</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>• Need for faster incident root-cause analysis due to rapid deployment and development cycles.
 • Integration challenges for diverse development teams needing GPU resources.</t>
         </is>
       </c>
-      <c r="T29" s="2" t="inlineStr">
+      <c r="W29" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small engineering teams
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE org
 • Fits teams that already own on-call but lack dedicated reliability headcount</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" s="2" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>ev_ca709ab1b570, ev_045b4447a1a0, ev_2219bee36788</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
         <is>
           <t>[status] https://status.thundercompute.com
+  Indicates production uptime monitoring.
 [homepage] https://www.thundercompute.com *
+  Explains core product and target customer.
 [fallback_page] https://www.thundercompute.com/about
+  Fetched from search result for additional context.
 [blog] https://www.thundercompute.com/blog
+  Product updates and engineering narrative.
 [fallback_page] https://www.thundercompute.com/contact
+  Fetched from search result for additional context.
 [docs] https://www.thundercompute.com/docs/vscode/quickstart *
+  Shows public API/integration/developer surface.
 [fallback_page] https://www.thundercompute.com/pricing
+  Fetched from search result for additional context.
 [seed_metadata] https://www.ycombinator.com/companies/thunder-compute *
-[careers] https://www.ycombinator.com/companies/thunder-compute/jobs</t>
+  Source list metadata (YC/CMU).
+[careers] https://www.ycombinator.com/companies/thunder-compute/jobs
+  Contains hiring/on-call/reliability signals.</t>
         </is>
       </c>
     </row>
@@ -3713,29 +4565,40 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G30" t="b">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H30" t="b">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>CTO or Head of Engineering</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>Helping your team build better AI agents with structured insights and performance analytics.</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Exploring AI Analytics Challenges for Engineering Teams</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>Hi,
 I’m reaching out to discuss the challenges many engineering teams face in deriving meaningful insights from AI agent interactions. As you might know, Voker’s AI analytics platform focuses on improving agent performance and connecting those interactions to key business outcomes. 
@@ -3744,52 +4607,68 @@
 Best regards,</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>Hi, I'm exploring insights on AI analytics challenges faced by engineering teams. Let's connect!</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>What challenges are you facing in quantifying AI investment returns and agent performance?</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>Voker is an AI analytics platform focused on enhancing agent performance through structured insights, ideal for B2B clients, particularly small engineering teams.</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>• Need for analytics on AI agent performance
 • Difficulty in connecting agent interactions to business outcomes
 • Resource-intensive processes for gathering usage data</t>
         </is>
       </c>
-      <c r="T30" s="2" t="inlineStr">
+      <c r="W30" s="2" t="inlineStr">
         <is>
           <t>• Improved analytics on AI agent performance
 • Enhanced visibility of agent interactions related to business outcomes
 • Reduced resource intensity in gathering crucial usage data</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" s="2" t="inlineStr"/>
+      <c r="Y30" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>ev_b5c8598e597d, ev_2114c3889bee, ev_b5a6abacdd3e</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
         <is>
           <t>[docs] https://app.voker.ai/docs/overview *
+  Shows public API/integration/developer surface.
 [fallback_page] https://app.voker.ai/docs/resources/changelog
+  Fetched from search result for additional context.
 [fallback_page] https://cal.com/tyler-postle
+  Fetched from search result for additional context.
 [homepage] https://voker.ai *
+  Explains core product and target customer.
 [blog] https://voker.ai/blog
+  Product updates and engineering narrative.
 [search_result] https://voker.ai/blog-posts/putting-the-infinite-context-window-to-the-test
+  Discovered via web search fallback.
 [search_result] https://voker.ai/blog-posts/the-rise-of-the-agent-engineer
+  Discovered via web search fallback.
 [search_result] https://voker.ai/blog/do-llms-play-favorites
+  Discovered via web search fallback.
 [careers] https://voker.ai/blog/the-rise-of-the-agent-engineer
-[seed_metadata] https://www.ycombinator.com/companies/voker *</t>
+  Contains hiring/on-call/reliability signals.
+[seed_metadata] https://www.ycombinator.com/companies/voker *
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -3820,41 +4699,56 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G31" t="b">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H31" t="b">
         <v>1</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>CFO or Head of Revenue Operations</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Bailey Spell</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/bailey-spell-b487ab149</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>Streamline your billing operations with AI to improve cash flow and efficiency, while integrating seamlessly into your current CRM and accounting systems.</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>Exploring automation in billing? Let's connect!</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Automating Billing Operations with AI</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>Hi Bailey,
 I’m reaching out to discuss LedgerUp’s focus on automating complex billing and revenue operations with AI, especially within manufacturing and SaaS industries. Given the challenges of manual billing processes and the necessity for effective integration with payment systems, there is significant potential to enhance operational efficiency.
@@ -3863,54 +4757,72 @@
 Best regards,</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
+      <c r="S31" s="2" t="inlineStr">
         <is>
           <t>Exploring automation in billing? Let's connect!</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>What challenges do you face in automating your billing and revenue collection processes?</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t>LedgerUp is a B2B enterprise solution focusing on automating complex billing and revenue operations with AI, particularly for industries like manufacturing and SaaS. They offer significant API documentation and effective tool integration, indicating a strong fit for outreach.</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>• Challenges in manual billing processes
 • Need for integration with enterprise customers' payment systems
 • Handling overdue invoices effectively</t>
         </is>
       </c>
-      <c r="T31" s="2" t="inlineStr">
+      <c r="W31" s="2" t="inlineStr">
         <is>
           <t>• Streamlines billing operations with AI to improve cash flow and efficiency
 • Seamless integration with existing CRM and accounting systems
 • Automates the invoicing and collection processes, reducing manual efforts</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" s="2" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>ev_e962ccdea6d2, ev_a8c4fca62002</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
         <is>
           <t>[homepage] https://www.ledgerup.ai/ *
+  Explains core product and target customer.
 [docs] https://www.ledgerup.ai/compare/zapier
+  Shows public API/integration/developer surface.
 [careers] https://www.ledgerup.ai/customer-stories
+  Contains hiring/on-call/reliability signals.
 [search_result] https://www.ledgerup.ai/legal/privacy-policy
+  Discovered via web search fallback.
 [fallback_page] https://www.ledgerup.ai/pricing
+  Fetched from search result for additional context.
 [fallback_page] https://www.ledgerup.ai/product/automate-collections
+  Fetched from search result for additional context.
 [fallback_page] https://www.ledgerup.ai/product/automate-contract-to-cash
+  Fetched from search result for additional context.
 [fallback_page] https://www.ledgerup.ai/product/meet-ari
+  Fetched from search result for additional context.
 [fallback_page] https://www.ledgerup.ai/product/procurement-portal-automation
+  Fetched from search result for additional context.
 [fallback_page] https://www.ledgerup.ai/product/usage
+  Fetched from search result for additional context.
 [fallback_page] https://www.ledgerup.ai/solutions/manufacturing-ar
-[seed_metadata] https://www.ycombinator.com/companies/ledgerup *</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/ledgerup *
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -3941,41 +4853,56 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G32" t="b">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H32" t="b">
         <v>1</v>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>Product Manager or Technical Lead at Property Management Companies</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Bill Ulammandakh</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/bulam/</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>Consider enhancing your current operations with ProhostAI's API features, aimed at streamlining task management and guest interactions.</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>ProhostAI offers innovative property management software for short-term rentals. Let's connect!</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Exploring Property Management Efficiency with ProhostAI</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>Hi Bill,
 I'm reaching out to discuss how ProhostAI's property management software could help enhance your operations in the short-term rental market. Our solution addresses common challenges such as managing multiple properties efficiently, automating guest communication and task coordination, and seamlessly integrating with various property management tools.
@@ -3983,50 +4910,64 @@
 Looking forward to your insights.</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>Interested in how ProhostAI solves property management challenges—let's connect!</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>How do you currently handle communication and task management across multiple properties?</t>
         </is>
       </c>
-      <c r="R32" s="2" t="inlineStr">
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>ProhostAI provides property management software specifically designed for short-term rental managers. Their platform features real-time chat capabilities and automated task management, addressing efficiency and integration challenges in property management.</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>• Managing multiple properties efficiently
 • Automating guest communication and task coordination
 • Integrating various property management tools seamlessly</t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>• Enhances task automation for property management
 • Simplifies guest communication through integrated solutions
 • Supports API integrations for seamless tool usage</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>ev_3a66218016a4, ev_95dfeea084a3, ev_b0d808296e83</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
         <is>
           <t>[careers] https://app.dover.com/jobs/prohost *
+  Contains hiring/on-call/reliability signals.
 [fallback_page] https://feedback.prohost.ai
+  Fetched from search result for additional context.
 [homepage] https://www.prohost.ai *
+  Explains core product and target customer.
 [blog] https://www.prohost.ai/blog
+  Product updates and engineering narrative.
 [docs] https://www.prohost.ai/developers *
+  Shows public API/integration/developer surface.
 [fallback_page] https://www.prohost.ai/pricing
+  Fetched from search result for additional context.
 [fallback_page] https://www.prohost.ai/team-chat
-[seed_metadata] https://www.ycombinator.com/companies/prohostai</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/prohostai
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -4057,41 +4998,56 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G33" t="b">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H33" t="b">
         <v>1</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Head of Technology</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Codrut Lemeni</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/codrut-l-328331134</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>I noticed Educato's emphasis on AI-driven learning tools aligns with our goal at Emergent Delta to support small engineering teams navigating incident response. As your platform scales, integrating educational tools effectively can be critical. I’d like to understand how you're currently managing incident response amidst this growth.</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>Emergent Delta aligns with Educato's mission in AI-driven educational tools for efficiency. Let's connect!</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Exploring Incident Response Strategies for Educato</t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr">
+      <c r="R33" s="2" t="inlineStr">
         <is>
           <t>Hi Codrut, 
 I’ve examined Educato and your focus on AI-driven learning is commendable. As your platform scales, managing incident response effectively becomes more complex. Emergent Delta specializes in assisting small engineering teams with faster incident root-cause analysis, which might align with your needs. I'd like to know how you currently handle uptime and reliability in your exam prep platform as you expand. 
@@ -4099,54 +5055,73 @@
 [Your Name]</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
+      <c r="S33" s="2" t="inlineStr">
         <is>
           <t>Let's connect! I see potential synergies between Educato's tools and our incident response support at Emergent Delta.</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>What challenges do you face in maintaining uptime and reliability in your exam prep platform?</t>
         </is>
       </c>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="U33" s="2" t="inlineStr">
         <is>
           <t>Educato is an AI-driven exam preparation platform that enhances educational experiences through personalized study plans, practice tests, and extensive learning materials. The platform aims to make exam prep more accessible and effective for students worldwide, indicating a strong commitment to leveraging technology in education.</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>• Need for effective integration of educational tools with existing systems
 • Challenge in managing incident response in a rapidly scaling environment</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr">
+      <c r="W33" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small engineering teams
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE organization
 • Fits teams that already own on-call but lack dedicated reliability headcount</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" s="2" t="inlineStr"/>
+      <c r="Y33" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>ev_2a54cb75d0d7, ev_d7f5d2aca68f, ev_ebf5c5cbd796</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
         <is>
           <t>[homepage] https://www.educato.com *
+  Explains core product and target customer.
 [fallback_page] https://www.educato.com/about
+  Fetched from search result for additional context.
 [fallback_page] https://www.educato.com/about-us
+  Fetched from search result for additional context.
 [blog] https://www.educato.com/blog
+  Product updates and engineering narrative.
 [fallback_page] https://www.educato.com/company
+  Fetched from search result for additional context.
 [docs] https://www.educato.com/docs *
+  Shows public API/integration/developer surface.
 [fallback_page] https://www.educato.com/pricing
+  Fetched from search result for additional context.
 [status] https://www.educato.com/status
+  Indicates production uptime monitoring.
 [fallback_page] https://www.educato.com/team
+  Fetched from search result for additional context.
 [fallback_page] https://www.educato.com/terms
+  Fetched from search result for additional context.
 [seed_metadata] https://www.ycombinator.com/companies/educato
+  Source list metadata (YC/CMU).
 [careers] https://www.ycombinator.com/companies/educato-ai/jobs *
-[fallback_page] https://www.ycombinator.com/companies/educato/jobs</t>
+  Contains hiring/on-call/reliability signals.
+[fallback_page] https://www.ycombinator.com/companies/educato/jobs
+  Fetched from search result for additional context.</t>
         </is>
       </c>
     </row>
@@ -4177,29 +5152,44 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G34" t="b">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H34" t="b">
         <v>0</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>CTO or Product Manager</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>FirstWork's AI agents streamline frontline hiring processes—could we explore synergies with our incident response solutions for production engineering?</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Hi! I admire FirstWork's focus on automating hiring and compliance, and I see potential synergies with our incident response solutions. Let's connect!</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Exploring Synergies in Workforce Automation</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>Hello,
 I came across FirstWork and your innovative approach to automating workforce operations, particularly in document verification and onboarding. Many companies in your space face challenges like inefficient hiring processes and compliance risks due to document errors. Our product, Emergent Delta, aids production-critical software teams by facilitating faster incident root-cause analysis, which can complement your solutions by ensuring seamless operational effectiveness.
@@ -4207,53 +5197,70 @@
 Best regards,</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>Hi! I admire FirstWork's focus on automating hiring and compliance, and I see potential synergies with our incident response solutions. Let's connect!</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>What improvements are you seeking in your hiring and compliance processes?</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>FirstWork provides AI-powered solutions aimed at workforce operations, particularly focusing on document verification and automation of hiring and onboarding processes.</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>• Inefficient hiring processes
 • Compliance risks due to document errors
 • Long onboarding times for frontline workers</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t>• AI agents streamline onboarding and hiring, reducing time to productivity.
 • Enhances compliance by minimizing document errors with automated verifications.
 • Improves operational efficiency through automation of repetitive tasks.</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" s="2" t="inlineStr"/>
+      <c r="Y34" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>ev_213cc8ce2ef7, ev_a98f727b7181, ev_1ba46775a35f</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
         <is>
           <t>[status] https://status.firstwork.com
+  Indicates production uptime monitoring.
 [homepage] https://www.firstwork.com/ *
+  Explains core product and target customer.
 [fallback_page] https://www.firstwork.com/about-us
+  Fetched from search result for additional context.
 [fallback_page] https://www.firstwork.com/ai-recollection-agent
+  Fetched from search result for additional context.
 [fallback_page] https://www.firstwork.com/blog
+  Fetched from search result for additional context.
 [careers] https://www.firstwork.com/case-studies/how-a-major-live-events-operator-automated-hiring-and-credentialing-end-to-end-with-ai-native-agents *
+  Contains hiring/on-call/reliability signals.
 [fallback_page] https://www.firstwork.com/case-studies/how-a-retail-chain-accelerated-multi-store-hiring-with-firstwork
+  Fetched from search result for additional context.
 [docs] https://www.firstwork.com/document-agent *
+  Shows public API/integration/developer surface.
 [blog] https://www.firstwork.com/newsroom
+  Product updates and engineering narrative.
 [fallback_page] https://www.firstwork.com/terms-of-service
-[seed_metadata] https://www.ycombinator.com/companies/firstwork</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/firstwork
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -4284,37 +5291,52 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G35" t="b">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H35" t="b">
         <v>1</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
         <is>
           <t>Brandon Boehme</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/brandon-boehme/</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>Explore how Maven's voice payment infrastructure can streamline your customer transactions seamlessly.</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>Excited about Maven's voice payment solutions. Let's connect!</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Exploring Challenges in Payment Integration for Voice AI</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>Hi Brandon,
 I noticed that Maven provides a payment infrastructure specifically designed for voice AI agents, focusing on critical production needs in B2B environments. With the complexities around PCI compliance and the need for seamless payment integration into various platforms, these aspects can present significant challenges.
@@ -4323,50 +5345,65 @@
 Looking forward to your insights.</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
         <is>
           <t>Hi Brandon, I'm intrigued by Maven's work in payment infrastructure for voice AI. Let's connect to share insights!</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>What challenges do you face in integrating payments within your voice AI solutions?</t>
         </is>
       </c>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>Maven provides a payment infrastructure for voice AI agents, addressing production-critical B2B software needs, while ensuring seamless integration across platforms.</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>• Ensuring PCI compliance for voice transactions
 • Integrating payments seamlessly into various voice AI platforms</t>
         </is>
       </c>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="W35" s="2" t="inlineStr">
         <is>
           <t>• Payments infrastructure tailored for voice AI, enabling quick integration.
 • Focus on production-critical needs for B2B environments.
 • Support for multiple payment processors through a single integration.</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" s="2" t="inlineStr"/>
+      <c r="Y35" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>ev_6089594646e2, ev_ced7194653f4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.trymaven.com/ *
+  Shows public API/integration/developer surface.
 [fallback_page] https://docs.trymaven.com/introduction
+  Fetched from search result for additional context.
 [search_result] https://jobs.ashbyhq.com/goodmaven/967c9fa7-9caf-45f5-b259-00b551b29d6b
+  Discovered via web search fallback.
 [careers] https://jobs.ashbyhq.com/maven
+  Contains hiring/on-call/reliability signals.
 [search_result] https://jobs.ashbyhq.com/maven-agi/104c8312-2a9d-44c7-bb3c-0cdf8634f861
+  Discovered via web search fallback.
 [search_result] https://jobs.ashbyhq.com/maven-agi/9ad87881-5412-4ed8-8dfd-1383dc2f4522
+  Discovered via web search fallback.
 [search_result] https://jobs.ashbyhq.com/maven/1766ff90-20c1-4c28-b2d5-106b4f8a6701
+  Discovered via web search fallback.
 [homepage] https://trymaven.com *
-[seed_metadata] https://www.ycombinator.com/companies/maven</t>
+  Explains core product and target customer.
+[seed_metadata] https://www.ycombinator.com/companies/maven
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -4397,41 +5434,56 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G36" t="b">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H36" t="b">
         <v>1</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>Product Manager in Construction Tech</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Milind Sagaram</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/milind-sagaram</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>Helonic’s innovative use of AI could streamline incident analysis for teams handling complex construction projects.</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>Helonic's AI innovations could transform construction incident analysis. Would love to connect!</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>Inquiry on Drawing Analysis and Coordination Practices</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>Hi Milind,
 I came across Helonic, particularly your advancements in AI-powered construction drawing analysis. Your focus on improving on-call reliability and extensive API documentation stands out, especially given the high costs construction teams face from errors in drawings and coordination failures. It appears that your technology addresses significant pain points in the industry, potentially reducing costly rework and enhancing project execution.
@@ -4439,51 +5491,68 @@
 Looking forward to your insights.</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>Hi Milind, I'm interested in Helonic's AI-driven approach to construction drawing analysis and would love to connect!</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>How are you currently handling drawing analysis and coordination issues in your projects?</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr">
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>Helonic is a B2B startup specializing in AI-powered construction drawing analysis, providing solutions to reduce errors and improve coordination in construction projects.</t>
         </is>
       </c>
-      <c r="S36" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>• Construction teams face high costs due to errors in drawings.
 • Coordination failures lead to issues in project execution and increased RFIs.</t>
         </is>
       </c>
-      <c r="T36" s="2" t="inlineStr">
+      <c r="W36" s="2" t="inlineStr">
         <is>
           <t>• Improving drawing analysis to avoid costly rework.
 • Enhancing on-call reliability for project teams through AI-driven insights.</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" s="2" t="inlineStr"/>
+      <c r="Y36" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>ev_0234a2399866, ev_156943d40678, ev_2b8558e7a20b</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
         <is>
           <t>[homepage] https://helonic.com *
+  Explains core product and target customer.
 [fallback_page] https://helonic.com/blog
+  Fetched from search result for additional context.
 [fallback_page] https://helonic.com/blog/ai-plan-review-guide
+  Fetched from search result for additional context.
 [blog] https://helonic.com/blog/construction-rework-costs
+  Product updates and engineering narrative.
 [careers] https://helonic.com/blog/demolition-phase-drawing-review *
+  Contains hiring/on-call/reliability signals.
 [fallback_page] https://helonic.com/blog/hospitality-hotel-construction-coordination
+  Fetched from search result for additional context.
 [fallback_page] https://helonic.com/blog/mep-coordination-best-practices
+  Fetched from search result for additional context.
 [docs] https://helonic.com/blog/permit-set-vs-ifc-set-differences *
+  Shows public API/integration/developer surface.
 [status] https://helonic.com/status
+  Indicates production uptime monitoring.
 [seed_metadata] https://www.ycombinator.com/companies/helonic
-[fallback_page] https://www.ycombinator.com/companies/helonic/jobs</t>
+  Source list metadata (YC/CMU).
+[fallback_page] https://www.ycombinator.com/companies/helonic/jobs
+  Fetched from search result for additional context.</t>
         </is>
       </c>
     </row>
@@ -4514,41 +5583,52 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G37" t="b">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H37" t="b">
         <v>1</v>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Head of Engineering or Development Manager</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Inderpal Singh</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/inderpals</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>I noticed Substrate is automating healthcare revenue cycle functions; our tools can further enhance the reliability of your AI processes.</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
         <is>
           <t>Collaboration Opportunity to Enhance Revenue Cycle Automation</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>Hi Inderpal,
 I've been examining Substrate's efforts in automating healthcare revenue cycle management, particularly your focus on claims and appeals automation. Given the technical depth of your API documentation, there appears to be significant potential for enhancing the reliability of existing AI processes. Our solution, Emergent Delta, aligns with your goals by providing a faster, AI-assisted incident root-cause analysis tailored for smaller production engineering teams like yours.
@@ -4558,52 +5638,68 @@
 [Your Name]</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>Hi Inderpal, I admire Substrate's work on healthcare revenue cycle automation. I'd like to connect and discuss potential synergies.</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>What challenges are you currently facing in automating your revenue cycle processes?</t>
         </is>
       </c>
-      <c r="R37" s="2" t="inlineStr">
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>Substrate focuses on automating healthcare revenue cycle management processes through technical solutions aimed at claims and appeals automation. They offer comprehensive API documentation, signaling a detailed and potentially effective approach to revenue cycle automation.</t>
         </is>
       </c>
-      <c r="S37" s="2" t="inlineStr">
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>• Automating manual processes in healthcare reimbursements
 • Dealing with high denial rates in claims
 • Improving efficiency in revenue cycle management</t>
         </is>
       </c>
-      <c r="T37" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>• Potential to enhance existing automation capabilities
 • Opportunity to streamline claims processes further
 • Support for integration with existing API systems</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr"/>
+      <c r="Y37" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>ev_ab0b69d049db, ev_f778189be613, ev_671daa28a0e3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
         <is>
           <t>[homepage] https://www.substrateai.com/ *
+  Explains core product and target customer.
 [fallback_page] https://www.substrateai.com/blog
+  Fetched from search result for additional context.
 [fallback_page] https://www.substrateai.com/blog/introducing-the-substrate-appeals-agent-for-medical-records
+  Fetched from search result for additional context.
 [changelog] https://www.substrateai.com/changelog
+  Release discipline and operational change signals.
 [status] https://www.substrateai.com/claim-status
+  Indicates production uptime monitoring.
 [docs] https://www.substrateai.com/document-review *
+  Shows public API/integration/developer surface.
 [fallback_page] https://www.substrateai.com/healthcare-networks
+  Fetched from search result for additional context.
 [fallback_page] https://www.substrateai.com/terms
+  Fetched from search result for additional context.
 [seed_metadata] https://www.ycombinator.com/companies/substrate
-[careers] https://www.ycombinator.com/companies/substrate/jobs/ *</t>
+  Source list metadata (YC/CMU).
+[careers] https://www.ycombinator.com/companies/substrate/jobs/ *
+  Contains hiring/on-call/reliability signals.</t>
         </is>
       </c>
     </row>
@@ -4634,41 +5730,56 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G38" t="b">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H38" t="b">
         <v>1</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>Head of Operations or Product Manager</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Maximilian Arnold</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/arnold-max/</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>Are you looking to improve operational insights using AI-driven conversations with your team?</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>Are you looking to improve operational insights using AI-driven conversations with your team?</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Exploring Operational Insights at Ontora</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t>Hi Maximilian,
 I’m reaching out as I noticed Ontora focuses on leveraging AI agents for capturing organizational knowledge, which can be crucial for teams examining their workflows. Given the challenges of understanding operational efficiency and the need for automated insights from employee interactions, I believe there could be mutual insights.
@@ -4676,48 +5787,57 @@
 Could you share how your team currently handles operational knowledge and incident response?</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
+      <c r="S38" s="2" t="inlineStr">
         <is>
           <t>Hi Maximilian, I admire Ontora's work in AI-driven operational insights. Let's connect!</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>How does your team currently handle operational knowledge and incident response?</t>
         </is>
       </c>
-      <c r="R38" s="2" t="inlineStr">
+      <c r="U38" s="2" t="inlineStr">
         <is>
           <t>Ontora develops AI agents to capture organizational knowledge, aiding incident response in production environments. Their platform offers API integrations but lacks thorough evidence for its on-call capabilities.</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr">
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>• Teams struggling with understanding their workflows and operational efficiency
 • Companies needing automated insights from employee interviews</t>
         </is>
       </c>
-      <c r="T38" s="2" t="inlineStr">
+      <c r="W38" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small engineering teams
 • Surfaces hypotheses from logs and deploys without a full SRE team
 • Fits teams that own on-call but lack dedicated reliability resources</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" s="2" t="inlineStr"/>
+      <c r="Y38" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V38" s="2" t="inlineStr">
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.ontora.com
+  Shows public API/integration/developer surface.
 [homepage] https://ontora.com
+  Explains core product and target customer.
 [blog] https://ontora.com/sign-in?redirect_url=https%3A%2F%2Fontora.com%2Fblog
+  Product updates and engineering narrative.
 [careers] https://ontora.com/sign-in?redirect_url=https%3A%2F%2Fontora.com%2Fcareers
+  Contains hiring/on-call/reliability signals.
 [status] https://ontora.com/sign-in?redirect_url=https%3A%2F%2Fontora.com%2Fstatus
+  Indicates production uptime monitoring.
 [fallback_page] https://ontora.com/terms-of-service
-[seed_metadata] https://www.ycombinator.com/companies/ontora</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/ontora
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -4748,29 +5868,36 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G39" t="b">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H39" t="b">
         <v>0</v>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Head of engineering or CTO at B2B firms focusing on AI-enhanced product visibility</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
         <is>
           <t>Inquiry on Tracking AI Product Visibility</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr">
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>Hello,
 I noticed that The Prompting Company specializes in enhancing product visibility through AI-driven platforms like ChatGPT. This aligns well with the emerging need for B2B teams, especially smaller engineering groups, to efficiently manage product mentions and responses without extensive resources.
@@ -4780,50 +5907,64 @@
 Looking forward to your insights.</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr">
+      <c r="S39" s="2" t="inlineStr">
         <is>
           <t>Hi! Interested in how The Prompting Company enhances AI-driven product visibility.</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>How do you currently track and manage your product's mentions within AI-driven interactions?</t>
         </is>
       </c>
-      <c r="R39" s="2" t="inlineStr">
+      <c r="U39" s="2" t="inlineStr">
         <is>
           <t>The Prompting Company specializes in enhancing product visibility in AI-driven platforms like ChatGPT, providing significant benefits for companies looking to boost product mentions in AI interactions.</t>
         </is>
       </c>
-      <c r="S39" s="2" t="inlineStr">
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>• Need for enhanced AI-driven product visibility
 • Challenges in tracking product mentions across multiple AI models
 • Efficient incident management without a full SRE team</t>
         </is>
       </c>
-      <c r="T39" s="2" t="inlineStr">
+      <c r="W39" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small eng teams
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE org
 • Fits teams that already own on-call but lack dedicated reliability headcount</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" s="2" t="inlineStr"/>
+      <c r="Y39" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>ev_dd985f0fbd50, ev_f58354c2e327, ev_cd8a1f31e12d, ev_05296fc5979a, ev_3c6f11e6c491</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.promptingcompany.com/tutorial/quickstart-guide *
+  Shows public API/integration/developer surface.
 [homepage] https://promptingcompany.com/ *
+  Explains core product and target customer.
 [blog] https://promptingcompany.com/blog
+  Product updates and engineering narrative.
 [fallback_page] https://promptingcompany.com/pricing *
+  Fetched from search result for additional context.
 [status] https://status.promptingcompany.com
+  Indicates production uptime monitoring.
 [fallback_page] https://techcrunch.com/2025/10/30/the-prompting-company-snags-6-5m-to-help-products-get-mentioned-in-chatgpt-and-other-ai-apps/ *
+  Fetched from search result for additional context.
 [careers] https://www.workatastartup.com/companies/the-prompting-company *
-[seed_metadata] https://www.ycombinator.com/companies/the-prompting-company</t>
+  Contains hiring/on-call/reliability signals.
+[seed_metadata] https://www.ycombinator.com/companies/the-prompting-company
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -4854,41 +5995,56 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G40" t="b">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H40" t="b">
         <v>1</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>VP of Engineering</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Daniel Han</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/danielhanchen</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Explore how Unsloth can streamline your team's local model training and improve operational efficiency without the need for complex infrastructure.</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>Interested in how Unsloth can enhance local model training for your team?</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>How is your team handling root-cause analysis?</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="R40" s="2" t="inlineStr">
         <is>
           <t>Hi Daniel,
 I came across Unsloth AI and noticed your focus on providing a local model training platform accessible via API. Your solution seems particularly relevant for companies aiming to optimize model training without the overhead of complex infrastructure.
@@ -4898,69 +6054,102 @@
 [Your Name]</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t>Hi Daniel, I'd love to connect and discuss how Unsloth AI is advancing local model training!</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>How is your team currently handling incident response and root-cause analysis?</t>
         </is>
       </c>
-      <c r="R40" s="2" t="inlineStr">
+      <c r="U40" s="2" t="inlineStr">
         <is>
           <t>Unsloth AI offers a local model training platform for developers, accessible through an API, with comprehensive documentation related to its features. It appears to target B2B sectors, aligning with production-critical software solutions. However, it lacks explicit mention of an on-call setup, which is noted as a potential concern.</t>
         </is>
       </c>
-      <c r="S40" s="2" t="inlineStr">
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>• Need for faster incident root-cause analysis
 • Limited reliability resources despite meeting demand
 • Operations running at capacity without dedicated SRE teams</t>
         </is>
       </c>
-      <c r="T40" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small eng teams
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE org
 • Fits teams that already own on-call but lack dedicated reliability headcount</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr"/>
+      <c r="Y40" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V40" s="2" t="inlineStr">
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>ev_e16173b48204, ev_ea62b51462ee, ev_c633bd26352c</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
         <is>
           <t>[search_result] http://job-boards.greenhouse.io/authenticx/jobs/4210044009
+  Discovered via web search fallback.
 [search_result] http://job-boards.greenhouse.io/mirakllabs/jobs/5361929004
+  Discovered via web search fallback.
 [search_result] https://apply.workable.com/aion/j/C3EC0F174E/
+  Discovered via web search fallback.
 [search_result] https://apply.workable.com/grnet-sa/j/A9625A85DC
+  Discovered via web search fallback.
 [search_result] https://job-boards.greenhouse.io/icapitalnetwork/jobs/8440665002?gh_src=Blind
+  Discovered via web search fallback.
 [search_result] https://job-boards.greenhouse.io/mirakllabs/jobs/5361929004?gh_src=0043172a4us
+  Discovered via web search fallback.
 [search_result] https://jobs.ashbyhq.com/inferact/9470565b-c62d-4de9-8b87-26d525ecec49
+  Discovered via web search fallback.
 [search_result] https://jobs.ashbyhq.com/sensmore/f10f3646-7a5b-43b5-a68e-d50e43c02af3
+  Discovered via web search fallback.
 [homepage] https://unsloth.ai *
+  Explains core product and target customer.
 [fallback_page] https://unsloth.ai/about
+  Fetched from search result for additional context.
 [fallback_page] https://unsloth.ai/blog/reintroducing
+  Fetched from search result for additional context.
 [fallback_page] https://unsloth.ai/docs
+  Fetched from search result for additional context.
 [fallback_page] https://unsloth.ai/docs/basics/api
+  Fetched from search result for additional context.
 [fallback_page] https://unsloth.ai/docs/basics/claude-code
+  Fetched from search result for additional context.
 [fallback_page] https://unsloth.ai/docs/de/grundlagen/claude-code
+  Fetched from search result for additional context.
 [search_result] https://unsloth.ai/docs/de/grundlagen/inference-and-deployment/deploying-llms-with-hugging-face-jobs
+  Discovered via web search fallback.
 [search_result] https://unsloth.ai/docs/fr/bases/inference-and-deployment/deploying-llms-with-hugging-face-jobs
+  Discovered via web search fallback.
 [search_result] https://unsloth.ai/docs/jp/ji-ben/inference-and-deployment/deploying-llms-with-hugging-face-jobs
+  Discovered via web search fallback.
 [fallback_page] https://unsloth.ai/docs/models/gemma-4
+  Fetched from search result for additional context.
 [fallback_page] https://unsloth.ai/docs/models/qwen3.6
+  Fetched from search result for additional context.
 [docs] https://unsloth.ai/docs/models/tutorials *
+  Shows public API/integration/developer surface.
 [fallback_page] https://unsloth.ai/docs/new/studio
+  Fetched from search result for additional context.
 [fallback_page] https://unsloth.ai/docs/new/studio/chat
+  Fetched from search result for additional context.
 [search_result] https://unsloth.ai/docs/zh/ji-chu/inference-and-deployment/deploying-llms-with-hugging-face-jobs
+  Discovered via web search fallback.
 [search_result] https://unsloth.ai/pricing
+  Discovered via web search fallback.
 [search_result] https://www.unsloth.ai/roadmap-yc
-[seed_metadata] https://www.ycombinator.com/companies/unsloth-ai *</t>
+  Discovered via web search fallback.
+[seed_metadata] https://www.ycombinator.com/companies/unsloth-ai *
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -4991,41 +6180,52 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="G41" t="b">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H41" t="b">
         <v>1</v>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>CTO or Head of Engineering in healthcare AI companies</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Saheed Akinbile</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Co-founder &amp; CTO</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/saheed-akinbile</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>Wondering how you can improve desktop automation? Minicor's platform could streamline processes and reduce maintenance efforts.</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Exploring Automation Challenges in Healthcare?</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr">
+      <c r="R41" s="2" t="inlineStr">
         <is>
           <t>Hi Saheed,
 I noticed that Minicor is focused on improving robotic process automation (RPA) in the healthcare sector. Given your commitment to scaling desktop automation solutions and the challenges associated with legacy systems, I believe there may be common ground for an insightful discussion.
@@ -5035,50 +6235,65 @@
 [Your Name]</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr">
+      <c r="S41" s="2" t="inlineStr">
         <is>
           <t>Hi Saheed, I'd love to connect to discuss automation challenges in healthcare and your work at Minicor.</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>How are you currently managing your desktop automation, and what challenges are you facing with maintenance and updates?</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr">
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t>Minicor offers a B2B RPA platform for desktop automation targeted at the healthcare sector, emphasizing fast deployment and reduced maintenance efforts through self-healing agents.</t>
         </is>
       </c>
-      <c r="S41" s="2" t="inlineStr">
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>• Need for faster deployment of robotic process automation in legacy systems
 • Challenges with maintaining traditional RPA scripts due to frequent updates</t>
         </is>
       </c>
-      <c r="T41" s="2" t="inlineStr">
+      <c r="W41" s="2" t="inlineStr">
         <is>
           <t>• AI-assisted incident root cause analysis
 • Faster deployment of automation solutions
 • Enhanced efficiency in managing legacy systems</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" s="2" t="inlineStr"/>
+      <c r="Y41" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>ev_d4a3c802bbc3, ev_6b5766c842ca, ev_c9483aef5e52</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.laminar.run/ *
+  Shows public API/integration/developer surface.
 [github] https://github.com/laminar-run
+  Technical footprint and engineering culture.
 [fallback_page] https://legal.laminar.run/terms-of-service
+  Fetched from search result for additional context.
 [homepage] https://www.minicor.com/ *
+  Explains core product and target customer.
 [blog] https://www.minicor.com/blog
+  Product updates and engineering narrative.
 [careers] https://www.minicor.com/careers
+  Contains hiring/on-call/reliability signals.
 [fallback_page] https://www.minicor.com/contact
+  Fetched from search result for additional context.
 [fallback_page] https://www.minicor.com/installs/desktop-service
-[seed_metadata] https://www.ycombinator.com/companies/minicor *</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/minicor *
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -5109,88 +6324,120 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G42" t="b">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H42" t="b">
         <v>1</v>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
         <is>
           <t>Milo Schwartz</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/miloaschwartz/</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>Explore how Pangolin's zero-trust architecture can enhance your remote access security and operational efficiency.</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Explore Pangolin's innovative zero-trust architecture for enhanced remote access security. Let's connect!</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
         <is>
           <t>Enhancing Remote Access Security with Zero Trust Architecture</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="R42" s="2" t="inlineStr">
         <is>
           <t>Hi Milo,\n\nI noticed that Pangolin focuses on zero-trust remote access, which is vital for enterprises facing increasing cybersecurity threats. Your identity-aware VPN solution aligns well with industry standards and addresses challenges like secure remote access and identity management amidst scalability concerns. The robust API documentation further enhances integration capabilities with existing systems. \n\nGiven your focus on overcoming the challenges of remote access infrastructure, I am curious about how you currently handle remote access for your engineering and operational teams.\n\nBest regards,\n[Your Name]</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr">
+      <c r="S42" s="2" t="inlineStr">
         <is>
           <t>Hi Milo, I admire Pangolin's zero-trust approach to remote access, especially its implications for security and operational efficiency. Let's connect!</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>How do you currently handle remote access for your engineering and operational teams?</t>
         </is>
       </c>
-      <c r="R42" s="2" t="inlineStr">
+      <c r="U42" s="2" t="inlineStr">
         <is>
           <t>Pangolin is a zero-trust remote access platform suitable for B2B enterprises, offering an identity-aware VPN solution. It meets production-critical software needs and includes robust API documentation, aligning with industry standards.</t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr">
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>• Need for secure remote access solutions
 • Integration of identity management across systems
 • Scalability challenges in remote access infrastructure</t>
         </is>
       </c>
-      <c r="T42" s="2" t="inlineStr">
+      <c r="W42" s="2" t="inlineStr">
         <is>
           <t>• Zero-trust security model ensuring strict access controls
 • API capabilities for seamless integration
 • Enhanced scalability for diverse team needs</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" s="2" t="inlineStr"/>
+      <c r="Y42" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>ev_d43a096db7fc, ev_52478183a8fc, ev_2420f25493cd</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.pangolin.net/ *
+  Shows public API/integration/developer surface.
 [fallback_page] https://docs.pangolin.net/careers/join-us
+  Fetched from search result for additional context.
 [github] https://github.com/fosrl/pangolin
+  Technical footprint and engineering culture.
 [homepage] https://pangolin.net *
+  Explains core product and target customer.
 [careers] https://pangolin.net/careers *
+  Contains hiring/on-call/reliability signals.
 [fallback_page] https://pangolin.net/news
+  Fetched from search result for additional context.
 [fallback_page] https://pangolin.net/news/1-18-release
+  Fetched from search result for additional context.
 [blog] https://pangolin.net/news/how-pangolin-works
+  Product updates and engineering narrative.
 [fallback_page] https://pangolin.net/news/pangolin-edge-devices-drop-in-remote-access
+  Fetched from search result for additional context.
 [status] https://status.pangolin.net
-[seed_metadata] https://www.ycombinator.com/companies/pangolin</t>
+  Indicates production uptime monitoring.
+[seed_metadata] https://www.ycombinator.com/companies/pangolin
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -5221,29 +6468,44 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G43" t="b">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H43" t="b">
         <v>0</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>CTO or Engineering Lead</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>Stagewise empowers engineers with coding agents; let’s discuss how Emergent Delta can enhance incident RCA in your critical workflows.</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>Stagewise empowers engineers with coding agents; let’s connect to enhance your incident RCA workflows.</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Enhancing Incident RCA with Emergent Delta</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="R43" s="2" t="inlineStr">
         <is>
           <t>Hello,
 At Stagewise, we understand the complexities of incident root-cause analysis within your open-source environment. As your team navigates orchestration and code execution, the need for efficient incident analysis becomes crucial, especially without a dedicated Site Reliability Engineering team.
@@ -5253,53 +6515,70 @@
 [Your Name]</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr">
+      <c r="S43" s="2" t="inlineStr">
         <is>
           <t>Stagewise empowers engineers with coding agents; let’s connect to enhance your incident RCA workflows.</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>How does your team currently handle incident root-cause analysis when using your orchestration features?</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr">
+      <c r="U43" s="2" t="inlineStr">
         <is>
           <t>Stagewise serves as an open-source agentic IDE for developers, facilitating orchestration and code execution. Their integration of public APIs and comprehensive API documentation are strong indicators of their operational capabilities.</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr">
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>• Challenges in incident root-cause analysis given the nature of their platform
 • Need for efficient integration and support for small engineering teams without dedicated SRE
 • Potential limitations in on-call reliability due to size of the team and infrastructure</t>
         </is>
       </c>
-      <c r="T43" s="2" t="inlineStr">
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small engineering teams
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE org
 • Fits teams that already own on-call but lack dedicated reliability headcount</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr"/>
+      <c r="Y43" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>ev_5f113863693e, ev_6dfa1513cbf0, ev_1a4a6bd609a8, ev_4b6a97fe6308, ev_e48f242778d9</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.stagewise.io *
+  Shows public API/integration/developer surface.
 [github] https://github.com/stagewise-io/stagewise *
+  Technical footprint and engineering culture.
 [homepage] https://stagewise.io *
+  Explains core product and target customer.
 [careers] https://stagewise.io/mission
+  Contains hiring/on-call/reliability signals.
 [blog] https://stagewise.io/news
+  Product updates and engineering narrative.
 [fallback_page] https://stagewise.io/news/becoming-the-open-source-agentic-ide *
+  Fetched from search result for additional context.
 [fallback_page] https://stagewise.io/news/release-week-april-27-3 *
+  Fetched from search result for additional context.
 [fallback_page] https://stagewise.io/news/release-week-may-11-17
+  Fetched from search result for additional context.
 [fallback_page] https://stagewise.io/news/release-week-may-4-10
+  Fetched from search result for additional context.
 [fallback_page] https://stagewise.io/news/smart-approvals-deep-dive
-[seed_metadata] https://www.ycombinator.com/companies/stagewise</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/stagewise
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -5330,41 +6609,52 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G44" t="b">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H44" t="b">
         <v>1</v>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>Technical Lead or Product Manager from a small to medium software startup with a firm reliance on CRM tools.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Matt Riley</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Founder/CEO</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/matthewriley/</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>Explore how Fixture's AI-driven CRM solutions can streamline your customer engagement processes while integrating seamlessly with your existing systems.</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Understanding Your CRM Needs</t>
         </is>
       </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="R44" s="2" t="inlineStr">
         <is>
           <t>Hi Matt,
 I noticed that Fixture is designed with modern startups in mind, particularly with developer-oriented features such as robust APIs and automated data capture. These capabilities are beneficial for small engineering teams focused on optimizing workflows and maintaining updated CRM data without extensive manual effort.
@@ -5374,49 +6664,63 @@
 [Your Name]</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr">
+      <c r="S44" s="2" t="inlineStr">
         <is>
           <t>Hi Matt, I admire Fixture's approach to automating CRM for startups. Would love to connect and discuss customer engagement challenges.</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>What specific challenges do you encounter in managing customer interactions and ensuring data accuracy across your existing tools?</t>
         </is>
       </c>
-      <c r="R44" s="2" t="inlineStr">
+      <c r="U44" s="2" t="inlineStr">
         <is>
           <t>Fixture is an AI-first CRM tailored for startups, focused on enhancing customer interaction management through automated data capture and AI-driven insights.</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr">
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>• Need for effective customer interaction management amid growing customer data.
 • Challenges in keeping CRM data updated without manual effort.</t>
         </is>
       </c>
-      <c r="T44" s="2" t="inlineStr">
+      <c r="W44" s="2" t="inlineStr">
         <is>
           <t>• Developer-oriented features like robust APIs for integration.
 • Automated data capture from tools like email and Slack, reducing manual work.
 • AI-driven insights to streamline customer engagement workflows.</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" s="2" t="inlineStr"/>
+      <c r="Y44" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V44" s="2" t="inlineStr">
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>ev_eec1aad0a2ba, ev_a9699a72d6e5, ev_95c56a37a5d5, ev_4595169df6b7</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
         <is>
           <t>[homepage] https://fixture.app *
+  Explains core product and target customer.
 [docs] https://fixture.app/docs *
+  Shows public API/integration/developer surface.
 [careers] https://jobs.ashbyhq.com/Crusoe/a24af26b-2891-49fd-b442-e65151ae8572
+  Contains hiring/on-call/reliability signals.
 [search_result] https://jobs.ashbyhq.com/Crusoe/acd7fce2-8ae3-4478-9628-5bd61a997a9e
+  Discovered via web search fallback.
 [search_result] https://jobs.ashbyhq.com/halter/145af6e0-bc0f-4b0a-863e-0fef01a8a6ec
+  Discovered via web search fallback.
 [search_result] https://jobs.ashbyhq.com/heron-power/293d9155-e4df-453f-80a3-5166daef6e83
+  Discovered via web search fallback.
 [status] https://status.fixture.app *
-[seed_metadata] https://www.ycombinator.com/companies/fixture</t>
+  Indicates production uptime monitoring.
+[seed_metadata] https://www.ycombinator.com/companies/fixture
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -5447,29 +6751,44 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G45" t="b">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H45" t="b">
         <v>0</v>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>Product Manager, SRE Lead</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>Improve your AI agent reliability and performance with our continuous evaluation and customization platform, specifically designed for production-critical environments.</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>Let's connect to exchange insights on optimizing AI reliability and performance!</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Exploring AI Agent Performance Optimization</t>
         </is>
       </c>
-      <c r="O45" s="2" t="inlineStr">
+      <c r="R45" s="2" t="inlineStr">
         <is>
           <t>Hello,
 I’m reaching out because I noticed that Carrot Labs is focused on enhancing AI agents through continuous learning and optimization. Your emphasis on managing data drift and improving reliability aligns closely with the needs of small engineering teams handling production-critical software.
@@ -5477,47 +6796,59 @@
 What challenges do you face in maintaining the performance of your AI agents in production?</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr">
+      <c r="S45" s="2" t="inlineStr">
         <is>
           <t>Hi, I'm interested in discussing AI performance optimization and your approaches at Carrot Labs.</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>What challenges do you face in maintaining the performance of your AI agents in production?</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr">
+      <c r="U45" s="2" t="inlineStr">
         <is>
           <t>Carrot Labs enhances AI agents through continuous learning and performance optimization, addressing critical needs in managing data drift and optimizing reliability for production environments.</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr">
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>• Difficulty maintaining agent performance over time due to data drift.
 • Optimization of AI tools to reduce latency and increase reliability in production environments.</t>
         </is>
       </c>
-      <c r="T45" s="2" t="inlineStr">
+      <c r="W45" s="2" t="inlineStr">
         <is>
           <t>• Continuous evaluation and retraining optimizes agents as data drifts, enhancing reliability.
 • Custom models are built using production data, optimizing for specific workloads.
 • Addresses latency and correctness, critical factors in reliability.</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" s="2" t="inlineStr"/>
+      <c r="Y45" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V45" s="2" t="inlineStr">
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>ev_99c579480542, ev_1601b85f921a, ev_3cc1b2a38b03</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
         <is>
           <t>[homepage] https://carrotlabs.ai *
+  Explains core product and target customer.
 [blog] https://carrotlabs.ai/blog
+  Product updates and engineering narrative.
 [careers] https://carrotlabs.ai/careers *
+  Contains hiring/on-call/reliability signals.
 [status] https://carrotlabs.ai/status
+  Indicates production uptime monitoring.
 [docs] https://platform.carrotlabs.ai/docs *
-[seed_metadata] https://www.ycombinator.com/companies/carrot-labs</t>
+  Shows public API/integration/developer surface.
+[seed_metadata] https://www.ycombinator.com/companies/carrot-labs
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -5548,29 +6879,44 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G46" t="b">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H46" t="b">
         <v>0</v>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>Engineering Manager or Head of SRE</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>If your team struggles with incident response and on-call burdens, IncidentFox could alleviate that pressure with its AI-powered capabilities. The platform not only enhances efficiency through automation but also integrates seamlessly with existing tools, making it ideal for small teams without dedicated SRE resources.</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>AI-powered incident management tailored for small engineering teams at IncidentFox.</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
         <is>
           <t>Exploring Incident Management Solutions for Small Teams</t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="R46" s="2" t="inlineStr">
         <is>
           <t>Hello,
 I’m reaching out as I believe that IncidentFox could greatly benefit from the integration of Emergent Delta’s AI-assisted incident RCA solution. Our platform is designed specifically for small engineering teams, aiming to enhance incident management through automation and effective integration with current tools. This can help address your need for rapid incident resolution and ease the burden on teams lacking dedicated SRE resources.
@@ -5578,51 +6924,66 @@
 Best regards,</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
+      <c r="S46" s="2" t="inlineStr">
         <is>
           <t>Let's connect to discuss AI-powered incident management strategies for small teams.</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>What are the biggest challenges your team faces in managing incidents and maintaining uptime?</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr">
+      <c r="U46" s="2" t="inlineStr">
         <is>
           <t>IncidentFox is a high-potential candidate for integrating Emergent Delta's AI-assisted incident RCA solution, designed for small engineering teams. The platform focuses on optimizing incident management through automation and integration with various tools, which helps address real-time incident response challenges efficiently.</t>
         </is>
       </c>
-      <c r="S46" s="2" t="inlineStr">
+      <c r="V46" s="2" t="inlineStr">
         <is>
           <t>• Need for rapid incident resolution in production environments.
 • Lack of dedicated SRE resources for small engineering teams.
 • Integration challenges with existing tools for incident management.</t>
         </is>
       </c>
-      <c r="T46" s="2" t="inlineStr">
+      <c r="W46" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small engineering teams.
 • Surfaces hypotheses from logs and runbooks without a full SRE org.
 • Fits teams that already own on-call but lack dedicated reliability headcount.</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" s="2" t="inlineStr"/>
+      <c r="Y46" t="inlineStr">
         <is>
           <t>no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V46" s="2" t="inlineStr">
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>ev_fca8dadd57d8, ev_db1a1b16ef49, ev_9950fc947b81</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
         <is>
           <t>[search_result] http://www.incidentfox.ai/
+  Discovered via web search fallback.
 [github] https://github.com/incidentfox/incidentfox
+  Technical footprint and engineering culture.
 [docs] https://incidentfox.mintlify.app/ *
+  Shows public API/integration/developer surface.
 [homepage] https://www.incidentfox.ai/ *
+  Explains core product and target customer.
 [blog] https://www.incidentfox.ai/blog/index.html
+  Product updates and engineering narrative.
 [fallback_page] https://www.incidentfox.ai/blog/why-internal-ai-sre-tools-fail.html
+  Fetched from search result for additional context.
 [fallback_page] https://www.incidentfox.ai/blog/why-we-built-incidentfox.html
+  Fetched from search result for additional context.
 [fallback_page] https://www.incidentfox.ai/support.html
-[seed_metadata] https://www.ycombinator.com/companies/brownie</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/brownie
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -5653,89 +7014,116 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G47" t="b">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H47" t="b">
         <v>1</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>CTO or Head of Engineering</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Tom Achache</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Founder/CTO</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/tom-achache/</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>Unisson's automation in customer-facing tasks complements Emergent Delta's AI-driven solutions for incident response, potentially enhancing operational efficiency while reducing workloads. Let's explore how your team currently addresses operational bottlenecks.</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>Unisson's focus on AI for customer-facing teams aligns with Emergent Delta's mission of enhancing incident response. Interested in discussing this further?</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
         <is>
           <t>Exploring AI Solutions for Incident Response</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr">
+      <c r="R47" s="2" t="inlineStr">
         <is>
           <t>Hi Tom,
 I noticed that Unisson prioritizes operational efficiency through AI agents that automate customer-facing tasks. This focus appears to align well with Emergent Delta's goal of improving incident root cause analysis for production-critical software environments.
 Given the challenges in incident response and maintaining high service reliability, I believe there may be substantial value in discussing how our AI-assisted solutions could enhance your existing processes. Could you share how your team currently handles operational bottlenecks in customer-facing roles and the impact on incident management?</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr">
+      <c r="S47" s="2" t="inlineStr">
         <is>
           <t>Unisson's automation in customer-facing roles aligns with Emergent Delta's mission. Let's connect to discuss further!</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>How does your team currently handle operational bottlenecks in customer-facing role tasks, and what impact does it have on incident management?</t>
         </is>
       </c>
-      <c r="R47" s="2" t="inlineStr">
+      <c r="U47" s="2" t="inlineStr">
         <is>
           <t>Unisson is a B2B software company specializing in automating customer-facing tasks using AI agents. Their solutions focus on enhancing operational efficiency and effectiveness in incident management, making them a strong candidate for AI-assisted incident response tools.</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr">
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>• Need for more efficient incident response and root-cause analysis.
 • Challenges with operational inefficiencies in customer-facing roles.
 • Requirement for maintaining high service reliability and accuracy in task execution.</t>
         </is>
       </c>
-      <c r="T47" s="2" t="inlineStr">
+      <c r="W47" s="2" t="inlineStr">
         <is>
           <t>• AI-assisted incident root cause analysis aligns with their need for efficient problem resolution.
 • Focus on operational efficiency complements their goal of reducing workloads on customer-facing teams.
 • Emergent Delta's capabilities can enhance their existing automation, ensuring reliability and uptime.</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" s="2" t="inlineStr"/>
+      <c r="Y47" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V47" s="2" t="inlineStr">
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>ev_00ee7bc56184, ev_e3ccc632ac36, ev_1740f425aa53</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
         <is>
           <t>[fallback_page] https://trust.unisson.ai
+  Fetched from search result for additional context.
 [search_result] https://trust.unisson.ai/?tab=securityControls
+  Discovered via web search fallback.
 [homepage] https://www.unisson.ai *
+  Explains core product and target customer.
 [fallback_page] https://www.unisson.ai/privacy-policy
+  Fetched from search result for additional context.
 [fallback_page] https://www.unisson.ai/terms-of-service
-[seed_metadata] https://www.ycombinator.com/companies/unisson</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/unisson
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -5766,78 +7154,107 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G48" t="b">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H48" t="b">
         <v>0</v>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>CTO or Head of Product</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>Moda's in-depth observability capabilities can enhance your AI agent monitoring, offering insights that reduce the time spent on incident analysis.</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>Enhance your AI monitoring with Moda's observability capabilities.</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
         <is>
           <t>Exploring AI Observability Solutions for Enhanced Incident Management</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="R48" s="2" t="inlineStr">
         <is>
           <t>Hi,
 I noticed that Moda focuses on providing AI observability solutions tailored for B2B environments, particularly addressing challenges like agent and tool failures. You're likely aware of how crucial it is to understand user intents that traditional monitoring may miss. Given your capabilities and robust API documentation, it seems you could substantially benefit from a solution that accelerates incident root-cause analysis in production-critical contexts.
 How do you currently monitor and resolve unexpected user intents or agent failures in your AI systems?</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr">
+      <c r="S48" s="2" t="inlineStr">
         <is>
           <t>I'd like to connect to discuss how AI observability can enhance your incident management strategy using Moda.</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>How do you currently monitor and resolve unexpected user intents or agent failures in your AI systems?</t>
         </is>
       </c>
-      <c r="R48" s="2" t="inlineStr">
+      <c r="U48" s="2" t="inlineStr">
         <is>
           <t>Moda provides tailored AI observability solutions for B2B environments, focusing on production-critical software needs. Their solutions include extensive documentation and capabilities for user-agent interaction, showcasing their readiness for technical integration and operational oversight.</t>
         </is>
       </c>
-      <c r="S48" s="2" t="inlineStr">
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>• Challenges in handling agent failures and tool failures
 • Understanding emergent user intents that traditional monitoring misses</t>
         </is>
       </c>
-      <c r="T48" s="2" t="inlineStr">
+      <c r="W48" s="2" t="inlineStr">
         <is>
           <t>• Enhances AI agent monitoring and observability capabilities
 • Offers insights that help reduce time spent on incident analysis
 • Facilitates faster resolution of unexpected user intents</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" s="2" t="inlineStr"/>
+      <c r="Y48" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V48" s="2" t="inlineStr">
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>ev_fc87089f31fb, ev_a55e4b495bd9, ev_24ecaacd6e8f</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.moda.dev *
+  Shows public API/integration/developer surface.
 [careers] https://jobs.ashbyhq.com/cernel/b8a254f3-9a3f-43e9-be69-6bcb08a267e0
+  Contains hiring/on-call/reliability signals.
 [search_result] https://jobs.ashbyhq.com/cernel/ecd149e6-ab70-4ad0-9c41-d60ba7fbe495
+  Discovered via web search fallback.
 [homepage] https://www.moda.dev/ *
+  Explains core product and target customer.
 [fallback_page] https://www.moda.dev/blog *
+  Fetched from search result for additional context.
 [blog] https://www.moda.dev/blog/cohorts
+  Product updates and engineering narrative.
 [fallback_page] https://www.moda.dev/blog/octolane
-[seed_metadata] https://www.ycombinator.com/companies/moda</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/moda
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -5868,41 +7285,52 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G49" t="b">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H49" t="b">
         <v>1</v>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>Head of Payments/Finance for Marketplaces</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Lotanna Ezeike</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>CEO, Co-founder</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/lottsnomad</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>Discover how Emergent Delta can enhance Grade's payment API ecosystem with faster incident root-cause analysis without needing a dedicated SRE team.</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
         <is>
           <t>Exploring Grade's Payment API Challenges</t>
         </is>
       </c>
-      <c r="O49" s="2" t="inlineStr">
+      <c r="R49" s="2" t="inlineStr">
         <is>
           <t>Hi Lotanna,
 At Emergent Delta, we specialize in providing AI-assisted incident root-cause analysis tailored for small engineering teams. Given Grade's focus on simplifying international payment compliance through your payout API, we understand the operational challenges you might face, especially around KYC and DAC7 compliance.
@@ -5914,50 +7342,64 @@
 Emergent Delta</t>
         </is>
       </c>
-      <c r="P49" s="2" t="inlineStr">
+      <c r="S49" s="2" t="inlineStr">
         <is>
           <t>Hi Lotanna, I’d like to connect to share insights on enhancing payment compliance and operational efficiency for marketplaces.</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>Can you describe the most challenging aspects you face regarding compliance and payment operations for creators?</t>
         </is>
       </c>
-      <c r="R49" s="2" t="inlineStr">
+      <c r="U49" s="2" t="inlineStr">
         <is>
           <t>Grade is a B2B company offering a payout API that simplifies creator payments, compliance, and operational tasks like KYC and tax reporting, particularly for marketplaces and agencies dealing with international transactions.</t>
         </is>
       </c>
-      <c r="S49" s="2" t="inlineStr">
+      <c r="V49" s="2" t="inlineStr">
         <is>
           <t>• Complexity in managing international payment compliance for a large number of creators.
 • Need for rapid resolution of compliance or payment-related issues to avoid service interruptions.
 • Desire to minimize engineering overhead associated with maintaining in-house payment solutions.</t>
         </is>
       </c>
-      <c r="T49" s="2" t="inlineStr">
+      <c r="W49" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small engineering teams.
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE org.
 • Fits teams that already own on-call but lack dedicated reliability headcount.</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" s="2" t="inlineStr"/>
+      <c r="Y49" t="inlineStr">
         <is>
           <t>no_seed_email</t>
         </is>
       </c>
-      <c r="V49" s="2" t="inlineStr">
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>ev_325622f57874, ev_db0bbb60ff96, ev_decefd00b37b</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
         <is>
           <t>[homepage] https://usegrade.com *
+  Explains core product and target customer.
 [fallback_page] https://usegrade.com/agencies
+  Fetched from search result for additional context.
 [blog] https://usegrade.com/blog
+  Product updates and engineering narrative.
 [careers] https://usegrade.com/blog/post/a-founder-s-guide-to-paying-international-contractors *
+  Contains hiring/on-call/reliability signals.
 [search_result] https://usegrade.com/blog/post/how-to-scale-ugc
+  Discovered via web search fallback.
 [search_result] https://usegrade.com/blog/post/why-paywalls-matter-more-than-you-think
+  Discovered via web search fallback.
 [docs] https://usegrade.com/marketplaces *
-[seed_metadata] https://www.ycombinator.com/companies/grade</t>
+  Shows public API/integration/developer surface.
+[seed_metadata] https://www.ycombinator.com/companies/grade
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -5988,29 +7430,44 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G50" t="b">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H50" t="b">
         <v>0</v>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>Head of Engineering or CTO</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>Chamber enhances GPU workload management—how does your team currently handle incident responses at scale?</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>Chamber enhances GPU workload management—how does your team currently handle incident responses at scale?</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
         <is>
           <t>Incident Response and GPU Optimization Inquiry</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="R50" s="2" t="inlineStr">
         <is>
           <t>Hello,
 I see that Chamber is focused on optimizing GPU infrastructure management for AI/ML, which aligns with our interests at Emergent Delta. Your AI-driven platform for autonomous workload monitoring and incident response could significantly benefit small engineering teams in maintaining production-critical uptime.
@@ -6019,48 +7476,67 @@
 Best regards,</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr">
+      <c r="S50" s="2" t="inlineStr">
         <is>
           <t>Chamber enhances GPU workload management—how does your team handle incident responses at scale?</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>What incident response tools does your team currently leverage for GPU infrastructure issues?</t>
         </is>
       </c>
-      <c r="R50" s="2" t="inlineStr">
+      <c r="U50" s="2" t="inlineStr">
         <is>
           <t>Chamber optimizes GPU infrastructure management for AI/ML teams with an AI-driven platform that autonomously manages workload monitoring, incident response, and debugging.</t>
         </is>
       </c>
-      <c r="S50" s="2" t="inlineStr">
+      <c r="V50" s="2" t="inlineStr">
         <is>
           <t>• Challenges in optimizing GPU infrastructure usage without human intervention leading to inefficiencies.
 • Difficulty maintaining seamless incident response for GPU workload issues.</t>
         </is>
       </c>
-      <c r="T50" s="2" t="inlineStr"/>
-      <c r="U50" t="inlineStr">
+      <c r="W50" s="2" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr"/>
+      <c r="Y50" t="inlineStr">
         <is>
           <t>no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V50" s="2" t="inlineStr">
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>ev_a7be5def91b0, ev_e52a1dea8315, ev_bc9ced35b7f5, ev_d16341f8ca35, ev_dab2a396df93</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.usechamber.io/
+  Shows public API/integration/developer surface.
 [fallback_page] https://docs.usechamber.io/introduction *
+  Fetched from search result for additional context.
 [status] https://status.usechamber.io
+  Indicates production uptime monitoring.
 [search_result] https://usechamber.io/
+  Discovered via web search fallback.
 [search_result] https://usechamber.io/blog/gpu-utilization-optimization-complete-guide
+  Discovered via web search fallback.
 [search_result] https://usechamber.io/compare
+  Discovered via web search fallback.
 [homepage] https://www.usechamber.io *
+  Explains core product and target customer.
 [fallback_page] https://www.usechamber.io/about *
+  Fetched from search result for additional context.
 [blog] https://www.usechamber.io/blog
+  Product updates and engineering narrative.
 [search_result] https://www.usechamber.io/blog/why-you-should-care-about-gpu-usage
+  Discovered via web search fallback.
 [fallback_page] https://www.usechamber.io/features *
+  Fetched from search result for additional context.
 [fallback_page] https://www.usechamber.io/pricing
-[seed_metadata] https://www.ycombinator.com/companies/chamber</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/chamber
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -6091,41 +7567,56 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G51" t="b">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H51" t="b">
         <v>1</v>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>Technical decision-maker in fintech</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Carmel Limcaoco</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/carmellimcaoco/</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>Considering Kita's focus on AI-native credit analysis, augmented incident response capabilities from Emergent Delta might integrate well with your current solutions.</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>Augmenting Kita's AI-native credit analysis with Emergent Delta could enhance incident response capabilities in your underwriting processes.</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
         <is>
           <t>Optimizing Incident Response for Your Credit Underwriting Operations</t>
         </is>
       </c>
-      <c r="O51" s="2" t="inlineStr">
+      <c r="R51" s="2" t="inlineStr">
         <is>
           <t>Hi Carmel, 
 As the founder of Kita, I’m sure you’re aware of the complexities involved in credit underwriting, particularly in managing fragmented borrower data and automating document verification processes. Emergent Delta is designed for small production engineering teams like yours and could significantly streamline incident root cause analysis, improving operational efficiency.
@@ -6135,50 +7626,66 @@
 [Your Name]</t>
         </is>
       </c>
-      <c r="P51" s="2" t="inlineStr">
+      <c r="S51" s="2" t="inlineStr">
         <is>
           <t>Hi Carmel, I'd love to connect and discuss how Emergent Delta can enhance incident response in your credit underwriting operations.</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>How are you currently managing the root cause analysis of incidents within your credit underwriting operations?</t>
         </is>
       </c>
-      <c r="R51" s="2" t="inlineStr">
+      <c r="U51" s="2" t="inlineStr">
         <is>
           <t>Kita is a B2B provider of API solutions focusing on document extraction and credit underwriting in emerging markets and underserved communities in the U.S. Their offerings include AI-powered products such as AI Credit Officer, AI Underwriter, and Kita Capture, which enhance the credit review process and support integration capabilities critical for production engineering teams.</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr">
+      <c r="V51" s="2" t="inlineStr">
         <is>
           <t>• Difficulty in efficiently managing fragmented borrower data for credit underwriting.
 • Challenges in automating document verification and fraud detection in lending processes.</t>
         </is>
       </c>
-      <c r="T51" s="2" t="inlineStr">
+      <c r="W51" s="2" t="inlineStr">
         <is>
           <t>• Emergent Delta can enhance your incident response capabilities while you automate and optimize your document handling and credit underwriting processes.
 • Our solution improves root cause analysis for incidents, streamlining your operational efforts and minimizing downtime.</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" s="2" t="inlineStr"/>
+      <c r="Y51" t="inlineStr">
         <is>
           <t>no_seed_email</t>
         </is>
       </c>
-      <c r="V51" s="2" t="inlineStr">
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>ev_3205ab0b277d, ev_a2118c3f7747, ev_4ab1d8391467, ev_3dacec845c5d, ev_20868f43b575</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
         <is>
           <t>[status] https://status.usekita.com
+  Indicates production uptime monitoring.
 [homepage] https://www.usekita.com *
+  Explains core product and target customer.
 [blog] https://www.usekita.com/blog
+  Product updates and engineering narrative.
 [docs] https://www.usekita.com/capture *
+  Shows public API/integration/developer surface.
 [careers] https://www.usekita.com/careers *
+  Contains hiring/on-call/reliability signals.
 [fallback_page] https://www.usekita.com/contact
+  Fetched from search result for additional context.
 [fallback_page] https://www.usekita.com/documentation *
+  Fetched from search result for additional context.
 [fallback_page] https://www.usekita.com/pricing
+  Fetched from search result for additional context.
 [fallback_page] https://www.usekita.com/solutions
-[seed_metadata] https://www.ycombinator.com/companies/kita *</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/kita *
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -6209,83 +7716,117 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G52" t="b">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H52" t="b">
         <v>0</v>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>CTO or Head of Engineering</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>Your AI agent governance can benefit from Emergent Delta's solutions to ensure faster incident response and robust security automatically integrated across all your tools. I’d like to understand your current challenges better.</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>Exploring how your AI governance can leverage solutions for faster incident responses and enhanced security.</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
         <is>
           <t>Inquiry on AI Agent Governance</t>
         </is>
       </c>
-      <c r="O52" s="2" t="inlineStr">
+      <c r="R52" s="2" t="inlineStr">
         <is>
           <t>Hello,
 I am reaching out to understand how Agentic Fabriq is managing the governance and security of AI agents within your organization. Given your focus on identity and permissioning solutions, I believe there's a significant opportunity to enhance incident response and maintain robust security measures across your tools. Our platform, Emergent Delta, is designed to assist teams like yours in navigating these challenges effectively.
 Could you share what challenges you specifically face with managing identity and access for AI agents within your organization?</t>
         </is>
       </c>
-      <c r="P52" s="2" t="inlineStr">
+      <c r="S52" s="2" t="inlineStr">
         <is>
           <t>Interested in discussing AI agent governance solutions that enhance incident response.</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>What challenges do you face with managing identity and access for AI agents within your organization?</t>
         </is>
       </c>
-      <c r="R52" s="2" t="inlineStr">
+      <c r="U52" s="2" t="inlineStr">
         <is>
           <t>Agentic Fabriq provides identity and permissioning solutions for AI agents, essential for ensuring secure management of AI interactions. With strong integration capabilities, it supports production-critical teams in regulating agent access, maintaining audit trails, and establishing precise permissions seamlessly with existing infrastructures.</t>
         </is>
       </c>
-      <c r="S52" s="2" t="inlineStr">
+      <c r="V52" s="2" t="inlineStr">
         <is>
           <t>• Difficulty in managing secure interactions for AI agents within existing infrastructure.
 • Challenges with establishing a governance and visibility layer for agent activity.</t>
         </is>
       </c>
-      <c r="T52" s="2" t="inlineStr">
+      <c r="W52" s="2" t="inlineStr">
         <is>
           <t>• Provides a secure platform for managing AI agents with identity and permissioning suitable for B2B customers.
 • Substantive API documentation facilitates integration with key third-party services, enhancing operational efficiency.
 • Targets production-critical systems, aligning its offerings with companies requiring strong governance and security for their operations.</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" s="2" t="inlineStr"/>
+      <c r="Y52" t="inlineStr">
         <is>
           <t>no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V52" s="2" t="inlineStr">
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>ev_3a66eb276c53, ev_616930e5cf8f, ev_2104fe302ca4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
         <is>
           <t>[homepage] https://www.agenticfabriq.com *
+  Explains core product and target customer.
 [fallback_page] https://www.agenticfabriq.com/about
+  Fetched from search result for additional context.
 [fallback_page] https://www.agenticfabriq.com/about-us
+  Fetched from search result for additional context.
 [blog] https://www.agenticfabriq.com/blog
+  Product updates and engineering narrative.
 [careers] https://www.agenticfabriq.com/careers
+  Contains hiring/on-call/reliability signals.
 [fallback_page] https://www.agenticfabriq.com/company
+  Fetched from search result for additional context.
 [docs] https://www.agenticfabriq.com/docs *
+  Shows public API/integration/developer surface.
 [fallback_page] https://www.agenticfabriq.com/pricing
+  Fetched from search result for additional context.
 [fallback_page] https://www.agenticfabriq.com/solutions
+  Fetched from search result for additional context.
 [status] https://www.agenticfabriq.com/status
+  Indicates production uptime monitoring.
 [fallback_page] https://www.agenticfabriq.com/team
+  Fetched from search result for additional context.
 [fallback_page] https://www.agenticfabriq.com/terms
-[seed_metadata] https://www.ycombinator.com/companies/agentic-fabriq *</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/agentic-fabriq *
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -6316,29 +7857,40 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G53" t="b">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H53" t="b">
         <v>0</v>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>DevOps Engineer</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>Archal's platform could substantially benefit your team's pre-deployment testing phases by ensuring AI agents behave reliably and efficiently, minimizing post-deployment failures.</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
         <is>
           <t>Pre-Deployment Testing Insights for AI Agents</t>
         </is>
       </c>
-      <c r="O53" s="2" t="inlineStr">
+      <c r="R53" s="2" t="inlineStr">
         <is>
           <t>Hi,
 I wanted to reach out regarding Archal's innovative platform that focuses on the pre-deployment evaluation of autonomous AI agents. Your team may benefit from detailed testing and tracing of agent behavior in a simulated environment, which helps to ensure reliability before production. This approach addresses the common pain points faced by software development teams, specifically in managing integration errors and ensuring that AI agents perform as expected.
@@ -6346,53 +7898,71 @@
 Best,</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr">
+      <c r="S53" s="2" t="inlineStr">
         <is>
           <t>Interested in your thoughts on pre-deployment testing for AI agents.</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>How do you currently ensure AI agents meet deployment requirements, and what challenges are you facing in pre-deployment evaluations?</t>
         </is>
       </c>
-      <c r="R53" s="2" t="inlineStr">
+      <c r="U53" s="2" t="inlineStr">
         <is>
           <t>Archal has developed a platform for pre-deployment evaluation of autonomous AI agents, utilizing stateful clones of existing systems to enable detailed testing and tracing of agent behavior prior to production deployment.</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr">
+      <c r="V53" s="2" t="inlineStr">
         <is>
           <t>• Ensuring AI agents are reliable and function as expected before deploying to production to avoid costly errors.
 • Managing integration errors and unexpected behaviors early in the development lifecycle to prevent deployment setbacks.</t>
         </is>
       </c>
-      <c r="T53" s="2" t="inlineStr">
+      <c r="W53" s="2" t="inlineStr">
         <is>
           <t>• Facilitates detailed testing of AI agents before production deployment.
 • Helps avoid costly post-deployment failures by ensuring reliability in simulated environments.
 • Enables thorough evaluation using real API surfaces and digital twins.</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" s="2" t="inlineStr"/>
+      <c r="Y53" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V53" s="2" t="inlineStr">
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>ev_a84b63d61e52, ev_45cc352b3c2a, ev_7c82d1740e55</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
         <is>
           <t>[search_result] https://archal.ai/docs/introduction
+  Discovered via web search fallback.
 [fallback_page] https://docs.archal.ai/clones/discord
+  Fetched from search result for additional context.
 [fallback_page] https://docs.archal.ai/clones/github
+  Fetched from search result for additional context.
 [fallback_page] https://docs.archal.ai/clones/google-workspace
+  Fetched from search result for additional context.
 [fallback_page] https://docs.archal.ai/clones/linear
+  Fetched from search result for additional context.
 [fallback_page] https://docs.archal.ai/clones/slack
+  Fetched from search result for additional context.
 [fallback_page] https://docs.archal.ai/clones/stripe
+  Fetched from search result for additional context.
 [fallback_page] https://docs.archal.ai/clones/supabase
+  Fetched from search result for additional context.
 [docs] https://docs.archal.ai/introduction *
+  Shows public API/integration/developer surface.
 [homepage] https://www.archal.ai *
+  Explains core product and target customer.
 [fallback_page] https://www.archal.ai/thesis
-[seed_metadata] https://www.ycombinator.com/companies/archal *</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/archal *
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -6423,29 +7993,44 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G54" t="b">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H54" t="b">
         <v>0</v>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>Engineering Manager or DevOps Lead</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>InsForge's backend infrastructure supports AI applications, making it suitable for production-critical environments where swift incident response is crucial.</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>InsForge's backend infrastructure supports AI applications for rapid incident response.</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
         <is>
           <t>Exploring Incident Response Challenges</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr">
+      <c r="R54" s="2" t="inlineStr">
         <is>
           <t>Hello,
 I hope this message finds you well. At InsForge, we recognize that many engineering teams face challenges with incident root cause analysis, especially in production-critical applications. Our platform is designed for AI-native developers, offering robust backend support that includes user authentication, database management, and storage solutions.
@@ -6453,54 +8038,73 @@
 What challenges do your engineering teams face in managing production incidents?</t>
         </is>
       </c>
-      <c r="P54" s="2" t="inlineStr">
+      <c r="S54" s="2" t="inlineStr">
         <is>
           <t>Hi, I’m exploring how teams manage production incidents and would love to connect.</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>What challenges do your engineering teams face in managing production incidents?</t>
         </is>
       </c>
-      <c r="R54" s="2" t="inlineStr">
+      <c r="U54" s="2" t="inlineStr">
         <is>
           <t>InsForge is a backend platform designed for AI-native developers, providing robust support for user authentication, database management, and storage solutions.</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr">
+      <c r="V54" s="2" t="inlineStr">
         <is>
           <t>• Need for faster incident root cause analysis for production-critical applications.
 • Lack of dedicated reliability resources despite having an on-call team.</t>
         </is>
       </c>
-      <c r="T54" s="2" t="inlineStr">
+      <c r="W54" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small eng teams
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE org
 • Fits teams that already own on-call but lack dedicated reliability headcount</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" s="2" t="inlineStr"/>
+      <c r="Y54" t="inlineStr">
         <is>
           <t>no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V54" s="2" t="inlineStr">
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>ev_d956f29e6c09, ev_6d6f5ac07610, ev_123189e221db, ev_8dbb40250c1d</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
         <is>
           <t>[fallback_page] https://docs.insforge.dev/core-concepts/ai/architecture
+  Fetched from search result for additional context.
 [docs] https://docs.insforge.dev/core-concepts/authentication/architecture *
+  Shows public API/integration/developer surface.
 [fallback_page] https://docs.insforge.dev/core-concepts/database/architecture
+  Fetched from search result for additional context.
 [fallback_page] https://docs.insforge.dev/core-concepts/database/pgvector
+  Fetched from search result for additional context.
 [fallback_page] https://docs.insforge.dev/core-concepts/functions/architecture
+  Fetched from search result for additional context.
 [fallback_page] https://docs.insforge.dev/core-concepts/realtime/architecture
+  Fetched from search result for additional context.
 [fallback_page] https://docs.insforge.dev/core-concepts/storage/architecture
+  Fetched from search result for additional context.
 [fallback_page] https://docs.insforge.dev/introduction
+  Fetched from search result for additional context.
 [github] https://github.com/InsForge/InsForge
+  Technical footprint and engineering culture.
 [homepage] https://insforge.dev *
+  Explains core product and target customer.
 [blog] https://insforge.dev/blog
+  Product updates and engineering narrative.
 [seed_metadata] https://www.ycombinator.com/companies/insforge *
-[status] https://x.com/AwokoyaD/status/2045784162842394768</t>
+  Source list metadata (YC/CMU).
+[status] https://x.com/AwokoyaD/status/2045784162842394768
+  Indicates production uptime monitoring.</t>
         </is>
       </c>
     </row>
@@ -6531,37 +8135,52 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G55" t="b">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H55" t="b">
         <v>1</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
         <is>
           <t>Aum Upadhyay</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/aum-u-517016269/</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>Please consider how Silmaril's self-healing security measures address AI-related vulnerabilities without the need for a full-scale SRE team.</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>Silmaril's innovative defense solutions for AI threats are impressive. Let's connect!</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
         <is>
           <t>Exploring AI Security Solutions</t>
         </is>
       </c>
-      <c r="O55" s="2" t="inlineStr">
+      <c r="R55" s="2" t="inlineStr">
         <is>
           <t>Hi Aum,
 I came across Silmaril's innovative approach to AI-assisted prompt injection defense, particularly in production-critical environments. Your self-healing mechanisms could be a major advantage for teams facing the pressure of maintaining uptime without extensive Site Reliability Engineering (SRE) resources.
@@ -6571,52 +8190,68 @@
 [Your Name]</t>
         </is>
       </c>
-      <c r="P55" s="2" t="inlineStr">
+      <c r="S55" s="2" t="inlineStr">
         <is>
           <t>Hi Aum, I admire Silmaril's focus on securing AI systems. Let's connect!</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>How does your team currently navigate AI-generated security threats within your production systems?</t>
         </is>
       </c>
-      <c r="R55" s="2" t="inlineStr">
+      <c r="U55" s="2" t="inlineStr">
         <is>
           <t>Silmaril develops AI-assisted prompt injection defense solutions aimed at securing production-critical environments. Their approach combines self-healing mechanisms and a well-documented API to enhance operational reliability and incident response. Positioned as an ideal customer for Emergent Delta, they address security challenges in environments with limited SRE resources.</t>
         </is>
       </c>
-      <c r="S55" s="2" t="inlineStr">
+      <c r="V55" s="2" t="inlineStr">
         <is>
           <t>• Need for enhanced security against complex AI threats
 • Lack of extensive SRE resources for continuous incident response
 • Pressure to maintain uptime and reliability in critical systems</t>
         </is>
       </c>
-      <c r="T55" s="2" t="inlineStr">
+      <c r="W55" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small engineering teams
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE org
 • Fits teams that already own on-call but lack dedicated reliability headcount</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" s="2" t="inlineStr"/>
+      <c r="Y55" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V55" s="2" t="inlineStr">
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>ev_fa566c94f963, ev_843f81fe3c49</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
         <is>
           <t>[search_result] http://silmaril.dev
+  Discovered via web search fallback.
 [fallback_page] https://blog.google/security/prompt-injections-web/
+  Fetched from search result for additional context.
 [fallback_page] https://silmaril.dev
+  Fetched from search result for additional context.
 [fallback_page] https://www.capsulesecurity.io/blog-post/cursechain
+  Fetched from search result for additional context.
 [fallback_page] https://www.forcepoint.com/blog/x-labs/indirect-prompt-injection-payloads
+  Fetched from search result for additional context.
 [homepage] https://www.silmaril.dev/ *
+  Explains core product and target customer.
 [docs] https://www.silmaril.dev/docs *
+  Shows public API/integration/developer surface.
 [status] https://www.silmaril.dev/status
+  Indicates production uptime monitoring.
 [fallback_page] https://www.silmaril.dev/terms
-[seed_metadata] https://www.ycombinator.com/companies/silmaril</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/silmaril
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -6647,29 +8282,40 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G56" t="b">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H56" t="b">
         <v>0</v>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>Operations Manager or CTO for Property Management Firms</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
         <is>
           <t>persona_only</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>Trellis can automate your rental operations, freeing you from the chaos of manual communication and coordination, and ensuring seamless execution even at scale.</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
         <is>
           <t>Understanding Operational Challenges in Property Management</t>
         </is>
       </c>
-      <c r="O56" s="2" t="inlineStr">
+      <c r="R56" s="2" t="inlineStr">
         <is>
           <t>Hello,
 I hope this message finds you well. I wanted to reach out to discuss the operational challenges faced in property management, especially concerning scaling and task coordination. Trellis offers AI-driven solutions that automate communication and manage tasks effectively, aiming to reduce operational chaos and lower costs associated with manual oversight.
@@ -6677,54 +8323,72 @@
 How do you currently handle operational scaling challenges in your property management processes?</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr">
+      <c r="S56" s="2" t="inlineStr">
         <is>
           <t>Hi, I’m exploring operational efficiencies in property management and would like to connect.</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>How do you currently handle operational scaling challenges in your property management processes?</t>
         </is>
       </c>
-      <c r="R56" s="2" t="inlineStr">
+      <c r="U56" s="2" t="inlineStr">
         <is>
           <t>Trellis is an AI-driven operations management software designed for short-term rental management, streamlining property management operations through integration with over 200 tools and emphasizing automation and team coordination.</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr">
+      <c r="V56" s="2" t="inlineStr">
         <is>
           <t>• Disorganized property management operations leading to missed communications.
 • High operational costs due to manual task management.
 • Difficulty scaling due to increasing property messages and turnovers.</t>
         </is>
       </c>
-      <c r="T56" s="2" t="inlineStr">
+      <c r="W56" s="2" t="inlineStr">
         <is>
           <t>• AI-driven automation for efficient operational management.
 • Integration with over 200 tools for seamless coordination.
 • Robust API integration to enhance existing tech stacks.</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" s="2" t="inlineStr"/>
+      <c r="Y56" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_contact; no_seed_email; no_linkedin_url</t>
         </is>
       </c>
-      <c r="V56" s="2" t="inlineStr">
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>ev_b6fdf05604c5, ev_c3b1fbcb1fad, ev_7411c4bd0d42, ev_6683494ef1cb, ev_ad5591656e52</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.trellistech.com
+  Shows public API/integration/developer surface.
 [fallback_page] https://docs.trellistech.com/changelog
+  Fetched from search result for additional context.
 [fallback_page] https://docs.trellistech.com/introduction *
+  Fetched from search result for additional context.
 [status] https://status.trellistech.com
+  Indicates production uptime monitoring.
 [search_result] https://trellistech.com/
+  Discovered via web search fallback.
 [search_result] https://trellistech.com/privacy
+  Discovered via web search fallback.
 [homepage] https://www.trellistech.com/ *
+  Explains core product and target customer.
 [careers] https://www.trellistech.com/about *
+  Contains hiring/on-call/reliability signals.
 [fallback_page] https://www.trellistech.com/api-terms *
+  Fetched from search result for additional context.
 [blog] https://www.trellistech.com/blog *
+  Product updates and engineering narrative.
 [search_result] https://www.trellistech.com/dpa
-[seed_metadata] https://www.ycombinator.com/companies/trellistech</t>
+  Discovered via web search fallback.
+[seed_metadata] https://www.ycombinator.com/companies/trellistech
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -6755,41 +8419,52 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G57" t="b">
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H57" t="b">
         <v>1</v>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>Head of Engineering or Product Development</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Yoeven D Khemlani</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/yoeven</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>Leverage your expertise in deterministic AI modeling to enhance incident response and streamline root-cause analysis workflows in your team.</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
         <is>
           <t>Exploring Incident Analysis Solutions for Engineering Teams</t>
         </is>
       </c>
-      <c r="O57" s="2" t="inlineStr">
+      <c r="R57" s="2" t="inlineStr">
         <is>
           <t>Hi Yoeven,  
 I noticed that Interfaze focuses on deterministic developer tasks crucial for small engineering teams, which positions you well in tackling incident root-cause analysis challenges. Many small teams like yours often struggle with effective tools tailored for their resource constraints, especially in the B2B sector. Given your expertise in AI modeling for this area, leveraging advanced APIs could significantly enhance incident response workflows.  
@@ -6800,54 +8475,74 @@
 [Your Company]</t>
         </is>
       </c>
-      <c r="P57" s="2" t="inlineStr">
+      <c r="S57" s="2" t="inlineStr">
         <is>
           <t>Hi Yoeven, I'd love to connect and discuss deterministic AI modeling in incident analysis for small engineering teams.</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>What specific challenges do you face in maintaining reliability and conducting incident analysis with your current team size?</t>
         </is>
       </c>
-      <c r="R57" s="2" t="inlineStr">
+      <c r="U57" s="2" t="inlineStr">
         <is>
           <t>Interfaze focuses on deterministic developer tasks crucial for small engineering teams, particularly in AI-driven incident root-cause analysis, making them a strong fit for Emergent Delta.</t>
         </is>
       </c>
-      <c r="S57" s="2" t="inlineStr">
+      <c r="V57" s="2" t="inlineStr">
         <is>
           <t>• Need for effective incident root-cause analysis tools that suit small engineering teams without the resources of larger SRE organizations.</t>
         </is>
       </c>
-      <c r="T57" s="2" t="inlineStr">
+      <c r="W57" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small eng teams
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE org
 • Fits teams that already own on-call but lack dedicated reliability headcount</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" s="2" t="inlineStr"/>
+      <c r="Y57" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V57" s="2" t="inlineStr">
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>ev_78d85c4fda08, ev_79882094be01, ev_e1efa5bff723, ev_82e5ba1c4679, ev_39b50517c480</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
         <is>
           <t>[github] https://github.com/JigsawStack
+  Technical footprint and engineering culture.
 [homepage] https://interfaze.ai *
+  Explains core product and target customer.
 [blog] https://interfaze.ai/blog *
+  Product updates and engineering narrative.
 [careers] https://interfaze.ai/careers
+  Contains hiring/on-call/reliability signals.
 [docs] https://interfaze.ai/docs *
+  Shows public API/integration/developer surface.
 [fallback_page] https://interfaze.ai/docs/audio/speech-to-text
+  Fetched from search result for additional context.
 [fallback_page] https://interfaze.ai/docs/faqs
+  Fetched from search result for additional context.
 [fallback_page] https://interfaze.ai/docs/guardrails
+  Fetched from search result for additional context.
 [fallback_page] https://interfaze.ai/docs/translation
+  Fetched from search result for additional context.
 [fallback_page] https://interfaze.ai/docs/vision/ocr
+  Fetched from search result for additional context.
 [fallback_page] https://interfaze.ai/docs/web/web-scraping
+  Fetched from search result for additional context.
 [status] https://status.interfaze.ai
+  Indicates production uptime monitoring.
 [seed_metadata] https://www.ycombinator.com/companies/interfaze *
-[fallback_page] https://yoeven.notion.site/Careers-at-Interfaze-ai-17595f7334d3809b8007c63dbc1ee2ce</t>
+  Source list metadata (YC/CMU).
+[fallback_page] https://yoeven.notion.site/Careers-at-Interfaze-ai-17595f7334d3809b8007c63dbc1ee2ce
+  Fetched from search result for additional context.</t>
         </is>
       </c>
     </row>
@@ -6878,41 +8573,56 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G58" t="b">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H58" t="b">
         <v>1</v>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>Engineering Manager</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>Oskar Kwaśniewski</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/okwasniewski/</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>Discover how TesterArmy’s AI-powered testing can enhance your software reliability and preempt critical issues.</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>Discover how TesterArmy's AI-driven testing can support effective software reliability.</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
         <is>
           <t>Inquiry on Your Automated Testing Practices</t>
         </is>
       </c>
-      <c r="O58" s="2" t="inlineStr">
+      <c r="R58" s="2" t="inlineStr">
         <is>
           <t>Hi Oskar,
 I'm reaching out to learn more about how TesterArmy leverages AI in your testing automation platform. Your focus on production-critical software and support for public API documentation aligns closely with the needs of engineering managers seeking reliable bug detection in real-time environments. 
@@ -6922,29 +8632,29 @@
 [Your Name]</t>
         </is>
       </c>
-      <c r="P58" s="2" t="inlineStr">
+      <c r="S58" s="2" t="inlineStr">
         <is>
           <t>Hi Oskar, I'm interested in how TesterArmy's AI is changing testing automation for B2B. Let's connect!</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>How do you currently manage the detection and resolution of bugs in your production environments?</t>
         </is>
       </c>
-      <c r="R58" s="2" t="inlineStr">
+      <c r="U58" s="2" t="inlineStr">
         <is>
           <t>TesterArmy offers an AI-assisted testing automation platform designed for B2B users. It focuses on ensuring the reliability of production-critical software while providing strong support for public API documentation and integrations.</t>
         </is>
       </c>
-      <c r="S58" s="2" t="inlineStr">
+      <c r="V58" s="2" t="inlineStr">
         <is>
           <t>• Automated testing required to preemptively catch bugs affecting end-users
 • Need to ensure high software reliability with limited SRE resources
 • Complex integration demands across varying environments</t>
         </is>
       </c>
-      <c r="T58" s="2" t="inlineStr">
+      <c r="W58" s="2" t="inlineStr">
         <is>
           <t>• AI-driven testing that mimics real-user interactions for software reliability
 • Integrations with GitHub and Vercel enhance CI/CD workflows
@@ -6953,23 +8663,39 @@
 • Supports remote operations, catering to distributed engineering teams</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" s="2" t="inlineStr"/>
+      <c r="Y58" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V58" s="2" t="inlineStr">
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>ev_cf7b8976d010, ev_cdb7cf0d5711, ev_415c48af9b1c, ev_f20b5cebcff5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.tester.army/ *
+  Shows public API/integration/developer surface.
 [fallback_page] https://docs.tester.army/api-reference/tester-army-api/projects/list-projects *
+  Fetched from search result for additional context.
 [fallback_page] https://docs.tester.army/get-started
+  Fetched from search result for additional context.
 [homepage] https://tester.army *
+  Explains core product and target customer.
 [blog] https://tester.army/blog
+  Product updates and engineering narrative.
 [careers] https://tester.army/pricing
+  Contains hiring/on-call/reliability signals.
 [fallback_page] https://tester.army/solutions/ai-app-testing
+  Fetched from search result for additional context.
 [fallback_page] https://tester.army/solutions/ecommerce
+  Fetched from search result for additional context.
 [fallback_page] https://tester.army/solutions/mobile
-[seed_metadata] https://www.ycombinator.com/companies/testerarmy *</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/testerarmy *
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -7000,37 +8726,48 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G59" t="b">
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H59" t="b">
         <v>1</v>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
         <is>
           <t>Ethan Byrd</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/etbyrd/</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>Discover how Primitive can enhance incident response capabilities without requiring extensive reliability resources.</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
         <is>
           <t>Exploring Incident Response Solutions with Primitive</t>
         </is>
       </c>
-      <c r="O59" s="2" t="inlineStr">
+      <c r="R59" s="2" t="inlineStr">
         <is>
           <t>Hi Ethan,
 I came across Primitive and noted your focus on providing email handling solutions tailored for operational integration in engineering systems. It's impressive how your platform automates both inbound and outbound email processes, making it a suitable fit for applications requiring reliable email services.
@@ -7038,59 +8775,87 @@
 What strategies do you employ to ensure the reliability and efficiency of your email processing system?</t>
         </is>
       </c>
-      <c r="P59" s="2" t="inlineStr">
+      <c r="S59" s="2" t="inlineStr">
         <is>
           <t>Hi Ethan, I'd like to connect to discuss how we can enhance incident response capabilities and email handling at Primitive.</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>How do you manage the reliability and efficiency of your email processing system?</t>
         </is>
       </c>
-      <c r="R59" s="2" t="inlineStr">
+      <c r="U59" s="2" t="inlineStr">
         <is>
           <t>Primitive is a B2B developer infrastructure provider specializing in email handling solutions through webhooks, suitable for operational integration in engineering environments.</t>
         </is>
       </c>
-      <c r="S59" s="2" t="inlineStr">
+      <c r="V59" s="2" t="inlineStr">
         <is>
           <t>• Streamlining email handling for customer-facing applications
 • Handling incident responses with limited dedicated SRE resources</t>
         </is>
       </c>
-      <c r="T59" s="2" t="inlineStr">
+      <c r="W59" s="2" t="inlineStr">
         <is>
           <t>• Automating email processes to improve operational efficiency
 • Integration capabilities tailored for engineering requirements
 • Support for applications needing reliable email uptime and delivery</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>• Mature enterprise with large dedicated SRE/reliability org</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
         <is>
           <t>no_seed_email</t>
         </is>
       </c>
-      <c r="V59" s="2" t="inlineStr">
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>ev_51289172023c, ev_2c40f60df9c5, ev_3483ac782476</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
         <is>
           <t>[search_result] https://apply.workable.com/threepeaks/j/308FBFB110/
+  Discovered via web search fallback.
 [search_result] https://apply.workable.com/threepeaks/j/E329B699C4/
+  Discovered via web search fallback.
 [search_result] https://jobs.ashbyhq.com/cartesia/30dd64e9-178e-43d8-afaa-13bb97baf45d
+  Discovered via web search fallback.
 [search_result] https://jobs.ashbyhq.com/cartesia/4400b6ac-f132-4551-8acc-cd1682a1e364
+  Discovered via web search fallback.
 [search_result] https://jobs.ashbyhq.com/cartesia/5ad70f8d-7515-476b-bb9d-11e5302475dc
+  Discovered via web search fallback.
 [search_result] https://jobs.ashbyhq.com/cartesia/c20f4644-c543-4ae2-9a0e-bc881a52b2f3?embed=js
+  Discovered via web search fallback.
 [search_result] https://jobs.eu.lever.co/quantinuum/bc6cd8c1-9720-4118-9520-62aa2acf668b
+  Discovered via web search fallback.
 [search_result] https://jobs.lever.co/gohighlevel/6a233482-ad60-47f2-8337-a75f4b802430
+  Discovered via web search fallback.
 [search_result] https://jobs.lever.co/jobgether/e5e4c0da-95bf-4c9b-a07a-8e8f30c083b6
+  Discovered via web search fallback.
 [search_result] https://jobs.lever.co/saga-xyz/2ba92c2a-8cbd-4d81-9995-8734d4536cd0
+  Discovered via web search fallback.
 [search_result] https://jobs.workable.com/company/4usnhqyUHUmRGehymBgxWe/jobs-at-nillion
+  Discovered via web search fallback.
 [search_result] https://jobs.workable.com/view/vQkDqkcmA6ArhCH3mEgJth/hybrid-software-engineering-technical-lead%2C-platform---primitives-%26-registry-in-boston-at-tetrascience
+  Discovered via web search fallback.
 [homepage] https://www.primitive.dev/ *
+  Explains core product and target customer.
 [docs] https://www.primitive.dev/docs *
+  Shows public API/integration/developer surface.
 [fallback_page] https://www.primitive.dev/docs/quickstart
+  Fetched from search result for additional context.
 [fallback_page] https://www.primitive.dev/privacy
+  Fetched from search result for additional context.
 [fallback_page] https://www.primitive.dev/terms
-[seed_metadata] https://www.ycombinator.com/companies/primitive</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/primitive
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -7121,37 +8886,52 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G60" t="b">
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H60" t="b">
         <v>1</v>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
         <is>
           <t>Maceo Cardinale Kwik</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/maceo-cardinale-kwik/</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>Enhance your team's incident management directly within Slack with Datost, optimizing root-cause analysis without needing a full SRE team.</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>I admire how Datost streamlines data analysis in Slack and I'm keen to connect to explore insights on incident management challenges.</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
         <is>
           <t>Streamline Incident Management with Data Integration</t>
         </is>
       </c>
-      <c r="O60" s="2" t="inlineStr">
+      <c r="R60" s="2" t="inlineStr">
         <is>
           <t>Hi Maceo,
 I’m reaching out to learn more about how Datost is leveraging data analytics within Slack for incident management. Given that Datost focuses on improving operational efficiency for small engineering teams handling on-call duties, I believe there’s a significant opportunity to discuss your current processes for incident root-cause analysis.
@@ -7164,49 +8944,62 @@
 [Your Contact Information]</t>
         </is>
       </c>
-      <c r="P60" s="2" t="inlineStr">
+      <c r="S60" s="2" t="inlineStr">
         <is>
           <t>Hi Maceo, I'd love to connect and discuss incident management processes at Datost, especially how you're integrating with Slack for data efficiency.</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>How is your team currently managing incident responses and extracting insights from operational data?</t>
         </is>
       </c>
-      <c r="R60" s="2" t="inlineStr">
+      <c r="U60" s="2" t="inlineStr">
         <is>
           <t>Datost is a B2B company providing an AI data analytics tool that integrates with Slack to streamline data analysis and incident management processes. It is designed for production-critical environments and aligns well with small engineering teams who manage on-call responsibilities but may lack dedicated reliability personnel. By integrating with major data warehouses and business tools, Datost can potentially enhance operational efficiency and root-cause analysis capabilities for these teams.</t>
         </is>
       </c>
-      <c r="S60" s="2" t="inlineStr">
+      <c r="V60" s="2" t="inlineStr">
         <is>
           <t>• Need for faster incident root-cause analysis
 • Desire to surface hypotheses from various operational logs
 • Lack of dedicated reliability headcount in small teams</t>
         </is>
       </c>
-      <c r="T60" s="2" t="inlineStr">
+      <c r="W60" s="2" t="inlineStr">
         <is>
           <t>• Faster incident root-cause analysis for small eng teams
 • Surfaces hypotheses from logs, deploys, and runbooks without a full SRE org
 • Fits teams that already own on-call but lack dedicated reliability headcount</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" s="2" t="inlineStr"/>
+      <c r="Y60" t="inlineStr">
         <is>
           <t>manual_review_required; no_seed_email</t>
         </is>
       </c>
-      <c r="V60" s="2" t="inlineStr">
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>ev_9b026a396909, ev_ba7746da3b21, ev_23ab987fb17e</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
         <is>
           <t>[homepage] https://www.datost.com *
+  Explains core product and target customer.
 [careers] https://www.datost.com/404
+  Contains hiring/on-call/reliability signals.
 [blog] https://www.datost.com/blog
+  Product updates and engineering narrative.
 [docs] https://www.datost.com/docs
+  Shows public API/integration/developer surface.
 [fallback_page] https://www.datost.com/docs/introduction *
+  Fetched from search result for additional context.
 [fallback_page] https://www.datost.com/support
-[seed_metadata] https://www.ycombinator.com/companies/datost *</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/datost *
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
@@ -7237,41 +9030,56 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G61" t="b">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H61" t="b">
         <v>1</v>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>Technical lead at B2B software companies or heads of engineering responsible for integrations and system reliability.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>Adina Goerres</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/adinagoerres</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>seed_team</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>Superglue's platform can dramatically streamline your API management processes, potentially cutting your integration setup time by a factor of ten compared to your current solutions.</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>Let's connect; I see an opportunity to simplify your system integrations with our AI-driven platform.</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
         <is>
           <t>Inquiry on Your Integration Challenges</t>
         </is>
       </c>
-      <c r="O61" s="2" t="inlineStr">
+      <c r="R61" s="2" t="inlineStr">
         <is>
           <t>Hi Adina,
 I hope this message finds you well. I wanted to reach out regarding Superglue's AI-driven integration platform, which addresses common challenges faced by companies in establishing quick and effective system integrations. Our solution has shown to reduce development time significantly while supporting multiple API types including REST and GraphQL.
@@ -7279,56 +9087,71 @@
 What specific difficulties have you faced in meeting integration demands rapidly and reliably using your current tools?</t>
         </is>
       </c>
-      <c r="P61" s="2" t="inlineStr">
+      <c r="S61" s="2" t="inlineStr">
         <is>
           <t>Let's connect; I see an opportunity to simplify your system integrations with our AI-driven platform.</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>What specific difficulties have you faced in meeting integration demands rapidly and reliably using your current tools?</t>
         </is>
       </c>
-      <c r="R61" s="2" t="inlineStr">
+      <c r="U61" s="2" t="inlineStr">
         <is>
           <t>Superglue offers an AI-driven platform that enables rapid enterprise system integrations with comprehensive governance and security features. It supports various API protocols, including REST, GraphQL, and SOAP, and is designed to minimize integration development time and streamline migrations from legacy systems. The platform is particularly advantageous for B2B enterprises requiring efficient integration solutions.</t>
         </is>
       </c>
-      <c r="S61" s="2" t="inlineStr">
+      <c r="V61" s="2" t="inlineStr">
         <is>
           <t>• Pressure to reduce time and complexity in setting up system integrations
 • Challenges in migrating from outdated integration platforms
 • Managing integration without heavy reliance on IT resources</t>
         </is>
       </c>
-      <c r="T61" s="2" t="inlineStr">
+      <c r="W61" s="2" t="inlineStr">
         <is>
           <t>• Significantly reduces integration development time and migration efforts
 • Provides comprehensive governance and security for integrations
 • Supports various API types and facilitates seamless integrations across platforms</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" s="2" t="inlineStr"/>
+      <c r="Y61" t="inlineStr">
         <is>
           <t>no_seed_email</t>
         </is>
       </c>
-      <c r="V61" s="2" t="inlineStr">
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>ev_804651ec2ca7, ev_b29471c309d9</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
         <is>
           <t>[docs] https://docs.superglue.cloud/
+  Shows public API/integration/developer surface.
 [fallback_page] https://docs.superglue.cloud/getting-started/introduction
+  Fetched from search result for additional context.
 [github] https://github.com/superglue-ai/superglue
+  Technical footprint and engineering culture.
 [homepage] https://superglue.ai *
+  Explains core product and target customer.
 [blog] https://superglue.ai/blog/
+  Product updates and engineering narrative.
 [fallback_page] https://superglue.ai/faq *
+  Fetched from search result for additional context.
 [fallback_page] https://superglue.ai/pricing
+  Fetched from search result for additional context.
 [fallback_page] https://superglue.ai/tnc
-[seed_metadata] https://www.ycombinator.com/companies/superglue</t>
+  Fetched from search result for additional context.
+[seed_metadata] https://www.ycombinator.com/companies/superglue
+  Source list metadata (YC/CMU).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V61"/>
+  <autoFilter ref="A1:AA61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>